--- a/homes.xlsx
+++ b/homes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V389"/>
+  <dimension ref="A1:V388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,7 +763,7 @@
         <v>1905</v>
       </c>
       <c r="N4" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O4" t="n">
         <v>110</v>
@@ -1269,7 +1269,7 @@
         <v>1920</v>
       </c>
       <c r="N10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O10" t="n">
         <v>138</v>
@@ -1441,7 +1441,7 @@
         <v>1910</v>
       </c>
       <c r="N12" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O12" t="n">
         <v>134</v>
@@ -1527,7 +1527,7 @@
         <v>1905</v>
       </c>
       <c r="N13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O13" t="n">
         <v>148</v>
@@ -1699,7 +1699,7 @@
         <v>1890</v>
       </c>
       <c r="N15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O15" t="n">
         <v>109</v>
@@ -1785,7 +1785,7 @@
         <v>1910</v>
       </c>
       <c r="N16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O16" t="n">
         <v>140</v>
@@ -1871,7 +1871,7 @@
         <v>1940</v>
       </c>
       <c r="N17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O17" t="n">
         <v>142</v>
@@ -2129,7 +2129,7 @@
         <v>1875</v>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
         <v>168</v>
@@ -2215,7 +2215,7 @@
         <v>1900</v>
       </c>
       <c r="N21" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O21" t="n">
         <v>144</v>
@@ -2301,7 +2301,7 @@
         <v>1895</v>
       </c>
       <c r="N22" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O22" t="n">
         <v>148</v>
@@ -2471,7 +2471,7 @@
         <v>1900</v>
       </c>
       <c r="N24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O24" t="n">
         <v>160</v>
@@ -2557,7 +2557,7 @@
         <v>1850</v>
       </c>
       <c r="N25" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O25" t="n">
         <v>160</v>
@@ -2643,7 +2643,7 @@
         <v>1900</v>
       </c>
       <c r="N26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O26" t="n">
         <v>162</v>
@@ -2729,7 +2729,7 @@
         <v>1910</v>
       </c>
       <c r="N27" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O27" t="n">
         <v>177</v>
@@ -2901,7 +2901,7 @@
         <v>1900</v>
       </c>
       <c r="N29" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O29" t="n">
         <v>124</v>
@@ -3073,7 +3073,7 @@
         <v>1940</v>
       </c>
       <c r="N31" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O31" t="n">
         <v>187</v>
@@ -3331,7 +3331,7 @@
         <v>1915</v>
       </c>
       <c r="N34" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O34" t="n">
         <v>168</v>
@@ -3497,7 +3497,7 @@
         <v>1976</v>
       </c>
       <c r="N36" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O36" t="n">
         <v>185</v>
@@ -3583,7 +3583,7 @@
         <v>1933</v>
       </c>
       <c r="N37" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O37" t="n">
         <v>201</v>
@@ -3669,7 +3669,7 @@
         <v>1900</v>
       </c>
       <c r="N38" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O38" t="n">
         <v>138</v>
@@ -3755,7 +3755,7 @@
         <v>1924</v>
       </c>
       <c r="N39" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O39" t="n">
         <v>155</v>
@@ -3841,7 +3841,7 @@
         <v>1899</v>
       </c>
       <c r="N40" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O40" t="n">
         <v>199</v>
@@ -4357,7 +4357,7 @@
         <v>1890</v>
       </c>
       <c r="N46" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O46" t="n">
         <v>151</v>
@@ -4443,7 +4443,7 @@
         <v>1900</v>
       </c>
       <c r="N47" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O47" t="n">
         <v>162</v>
@@ -4615,7 +4615,7 @@
         <v>1967</v>
       </c>
       <c r="N49" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O49" t="n">
         <v>170</v>
@@ -4961,7 +4961,7 @@
         <v>1986</v>
       </c>
       <c r="N53" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O53" t="n">
         <v>224</v>
@@ -5049,7 +5049,7 @@
         <v>1899</v>
       </c>
       <c r="N54" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O54" t="n">
         <v>208</v>
@@ -5479,7 +5479,7 @@
         <v>1930</v>
       </c>
       <c r="N59" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O59" t="n">
         <v>203</v>
@@ -5565,7 +5565,7 @@
         <v>1895</v>
       </c>
       <c r="N60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O60" t="n">
         <v>137</v>
@@ -5651,7 +5651,7 @@
         <v>1928</v>
       </c>
       <c r="N61" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O61" t="n">
         <v>226</v>
@@ -5950,17 +5950,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>217 Liberty Ave</t>
+          <t>603 Swede St</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>West Norriton</t>
+          <t>Norristown</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5969,46 +5969,46 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>19403</v>
+        <v>19401</v>
       </c>
       <c r="G65" t="n">
-        <v>359000</v>
+        <v>359900</v>
       </c>
       <c r="H65" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I65" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>NORRISTOWN</t>
+          <t>Norristown</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>1871</v>
+        <v>3528</v>
       </c>
       <c r="L65" t="n">
-        <v>8325</v>
+        <v>2088</v>
       </c>
       <c r="M65" t="n">
-        <v>1950</v>
+        <v>1900</v>
       </c>
       <c r="N65" t="n">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="O65" t="n">
-        <v>192</v>
+        <v>102</v>
       </c>
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>Contingent</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/West-Norriton/217-Liberty-Ave-19403/home/39073330</t>
+          <t>https://www.redfin.com/PA/Norristown/603-Swede-St-19401/home/49749419</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -6018,11 +6018,11 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>PAMC2188204</t>
+          <t>PAMC2187832</t>
         </is>
       </c>
       <c r="U65" t="n">
-        <v>359000</v>
+        <v>359900</v>
       </c>
       <c r="V65" t="n">
         <v>0</v>
@@ -6036,12 +6036,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>603 Swede St</t>
+          <t>908 New Hope St</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6058,33 +6058,33 @@
         <v>19401</v>
       </c>
       <c r="G66" t="n">
-        <v>359900</v>
+        <v>364900</v>
       </c>
       <c r="H66" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I66" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Norristown</t>
+          <t>NORRISTOWN</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>3528</v>
+        <v>1812</v>
       </c>
       <c r="L66" t="n">
-        <v>2088</v>
+        <v>8276</v>
       </c>
       <c r="M66" t="n">
-        <v>1900</v>
+        <v>1957</v>
       </c>
       <c r="N66" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O66" t="n">
-        <v>102</v>
+        <v>201</v>
       </c>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Norristown/603-Swede-St-19401/home/49749419</t>
+          <t>https://www.redfin.com/PA/Norristown/908-New-Hope-St-19401/home/38111955</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -6104,14 +6104,14 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>PAMC2187832</t>
+          <t>PAMC2186026</t>
         </is>
       </c>
       <c r="U66" t="n">
-        <v>359900</v>
+        <v>384900</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>-20000</v>
       </c>
     </row>
     <row r="67">
@@ -6122,17 +6122,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>908 New Hope St</t>
+          <t>503 Bunker Hill Rd</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Norristown</t>
+          <t>Harleysville</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6141,38 +6141,38 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>19401</v>
+        <v>19438</v>
       </c>
       <c r="G67" t="n">
-        <v>364900</v>
+        <v>365000</v>
       </c>
       <c r="H67" t="n">
         <v>3</v>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>NORRISTOWN</t>
+          <t>TOWAMENCIN CONDOS</t>
         </is>
       </c>
       <c r="K67" t="n">
-        <v>1812</v>
-      </c>
-      <c r="L67" t="n">
-        <v>8276</v>
-      </c>
+        <v>1703</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="n">
-        <v>1957</v>
+        <v>1974</v>
       </c>
       <c r="N67" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="O67" t="n">
-        <v>201</v>
-      </c>
-      <c r="P67" t="inlineStr"/>
+        <v>214</v>
+      </c>
+      <c r="P67" t="n">
+        <v>344</v>
+      </c>
       <c r="Q67" t="inlineStr">
         <is>
           <t>Active</t>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Norristown/908-New-Hope-St-19401/home/38111955</t>
+          <t>https://www.redfin.com/PA/Harleysville/503-Bunker-Hill-Rd-19438/home/201851047</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -6190,14 +6190,14 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>PAMC2186026</t>
+          <t>PAMC2193382</t>
         </is>
       </c>
       <c r="U67" t="n">
-        <v>384900</v>
+        <v>375000</v>
       </c>
       <c r="V67" t="n">
-        <v>-20000</v>
+        <v>-10000</v>
       </c>
     </row>
     <row r="68">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>503 Bunker Hill Rd</t>
+          <t>19 Stuart Dr #19</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Harleysville</t>
+          <t>East Norriton</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6227,10 +6227,10 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>19438</v>
+        <v>19401</v>
       </c>
       <c r="G68" t="n">
-        <v>365000</v>
+        <v>369000</v>
       </c>
       <c r="H68" t="n">
         <v>3</v>
@@ -6240,24 +6240,26 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>TOWAMENCIN CONDOS</t>
+          <t>STUARTS KEEP</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>1703</v>
-      </c>
-      <c r="L68" t="inlineStr"/>
+        <v>2239</v>
+      </c>
+      <c r="L68" t="n">
+        <v>2239</v>
+      </c>
       <c r="M68" t="n">
-        <v>1974</v>
+        <v>1999</v>
       </c>
       <c r="N68" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="O68" t="n">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="P68" t="n">
-        <v>344</v>
+        <v>250</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -6266,7 +6268,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Harleysville/503-Bunker-Hill-Rd-19438/home/201851047</t>
+          <t>https://www.redfin.com/PA/East-Norriton/19-Stuart-Dr-19401/unit-19/home/39131500</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -6276,14 +6278,14 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>PAMC2193382</t>
+          <t>PAMC2195942</t>
         </is>
       </c>
       <c r="U68" t="n">
-        <v>375000</v>
+        <v>369000</v>
       </c>
       <c r="V68" t="n">
-        <v>-10000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -6299,12 +6301,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>19 Stuart Dr #19</t>
+          <t>601 Bismark Way</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>East Norriton</t>
+          <t>King Of Prussia</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6313,10 +6315,10 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>19401</v>
+        <v>19406</v>
       </c>
       <c r="G69" t="n">
-        <v>369000</v>
+        <v>369900</v>
       </c>
       <c r="H69" t="n">
         <v>3</v>
@@ -6326,26 +6328,26 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>STUARTS KEEP</t>
+          <t>PRUSSIAN WOODS</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>2239</v>
+        <v>1560</v>
       </c>
       <c r="L69" t="n">
-        <v>2239</v>
+        <v>11805</v>
       </c>
       <c r="M69" t="n">
-        <v>1999</v>
+        <v>1978</v>
       </c>
       <c r="N69" t="n">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="O69" t="n">
-        <v>165</v>
+        <v>237</v>
       </c>
       <c r="P69" t="n">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -6354,7 +6356,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/East-Norriton/19-Stuart-Dr-19401/unit-19/home/39131500</t>
+          <t>https://www.redfin.com/PA/King-of-Prussia/601-Bismark-Way-19406/home/38959353</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -6364,11 +6366,11 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>PAMC2195942</t>
+          <t>PAMC2181522</t>
         </is>
       </c>
       <c r="U69" t="n">
-        <v>369000</v>
+        <v>369900</v>
       </c>
       <c r="V69" t="n">
         <v>0</v>
@@ -6377,7 +6379,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MLS Listing</t>
+          <t>PAST SALE</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6387,12 +6389,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>601 Bismark Way</t>
+          <t>652 Longwood Rd</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>King Of Prussia</t>
+          <t>Collegeville</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6401,48 +6403,48 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>19406</v>
+        <v>19426</v>
       </c>
       <c r="G70" t="n">
-        <v>369900</v>
+        <v>374900</v>
       </c>
       <c r="H70" t="n">
         <v>3</v>
       </c>
       <c r="I70" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>PRUSSIAN WOODS</t>
+          <t>CRANBERRY ESTATES</t>
         </is>
       </c>
       <c r="K70" t="n">
-        <v>1560</v>
+        <v>1536</v>
       </c>
       <c r="L70" t="n">
-        <v>11805</v>
+        <v>2577</v>
       </c>
       <c r="M70" t="n">
-        <v>1978</v>
+        <v>1995</v>
       </c>
       <c r="N70" t="n">
-        <v>104</v>
+        <v>1</v>
       </c>
       <c r="O70" t="n">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="P70" t="n">
-        <v>236</v>
+        <v>120</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/King-of-Prussia/601-Bismark-Way-19406/home/38959353</t>
+          <t>https://www.redfin.com/PA/Collegeville/652-Longwood-Rd-19426/home/38744176</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -6452,11 +6454,11 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>PAMC2181522</t>
+          <t>PAMC2194726</t>
         </is>
       </c>
       <c r="U70" t="n">
-        <v>369900</v>
+        <v>374900</v>
       </c>
       <c r="V70" t="n">
         <v>0</v>
@@ -6465,7 +6467,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PAST SALE</t>
+          <t>MLS Listing</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6475,12 +6477,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>652 Longwood Rd</t>
+          <t>105 Bonnie Lark Ct</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Collegeville</t>
+          <t>Chalfont</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6489,48 +6491,48 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>19426</v>
+        <v>18914</v>
       </c>
       <c r="G71" t="n">
-        <v>374900</v>
+        <v>375000</v>
       </c>
       <c r="H71" t="n">
         <v>3</v>
       </c>
       <c r="I71" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>CRANBERRY ESTATES</t>
+          <t>THE HIGHLANDS</t>
         </is>
       </c>
       <c r="K71" t="n">
-        <v>1536</v>
+        <v>1545</v>
       </c>
       <c r="L71" t="n">
-        <v>2577</v>
+        <v>2178</v>
       </c>
       <c r="M71" t="n">
-        <v>1995</v>
+        <v>1988</v>
       </c>
       <c r="N71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O71" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P71" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Collegeville/652-Longwood-Rd-19426/home/38744176</t>
+          <t>https://www.redfin.com/PA/Chalfont/105-Bonnie-Lark-Ct-18914/home/38921023</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -6540,11 +6542,11 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>PAMC2194726</t>
+          <t>PABU2132648</t>
         </is>
       </c>
       <c r="U71" t="n">
-        <v>374900</v>
+        <v>375000</v>
       </c>
       <c r="V71" t="n">
         <v>0</v>
@@ -6563,12 +6565,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>105 Bonnie Lark Ct</t>
+          <t>113 Susan Constant Ct #13</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Chalfont</t>
+          <t>Norristown</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6577,7 +6579,7 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>18914</v>
+        <v>19401</v>
       </c>
       <c r="G72" t="n">
         <v>375000</v>
@@ -6590,26 +6592,26 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>THE HIGHLANDS</t>
+          <t>COURT AT JAMESTOWNE</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>1545</v>
+        <v>1964</v>
       </c>
       <c r="L72" t="n">
-        <v>2178</v>
+        <v>1964</v>
       </c>
       <c r="M72" t="n">
         <v>1988</v>
       </c>
       <c r="N72" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O72" t="n">
-        <v>243</v>
+        <v>191</v>
       </c>
       <c r="P72" t="n">
-        <v>180</v>
+        <v>315</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -6618,7 +6620,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Chalfont/105-Bonnie-Lark-Ct-18914/home/38921023</t>
+          <t>https://www.redfin.com/PA/Norristown/113-Susan-Constant-Ct-19401/unit-13/home/38330241</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -6628,7 +6630,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>PABU2132648</t>
+          <t>PAMC2195858</t>
         </is>
       </c>
       <c r="U72" t="n">
@@ -6641,22 +6643,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MLS Listing</t>
+          <t>PAST SALE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>113 Susan Constant Ct #13</t>
+          <t>2206 Lenhart Rd</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Norristown</t>
+          <t>Colmar</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6665,48 +6667,46 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>19401</v>
+        <v>18915</v>
       </c>
       <c r="G73" t="n">
         <v>375000</v>
       </c>
       <c r="H73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I73" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>COURT AT JAMESTOWNE</t>
+          <t>Colmar</t>
         </is>
       </c>
       <c r="K73" t="n">
-        <v>1964</v>
+        <v>1813</v>
       </c>
       <c r="L73" t="n">
-        <v>1964</v>
+        <v>43560</v>
       </c>
       <c r="M73" t="n">
-        <v>1988</v>
+        <v>1950</v>
       </c>
       <c r="N73" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="O73" t="n">
-        <v>191</v>
-      </c>
-      <c r="P73" t="n">
-        <v>315</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Norristown/113-Susan-Constant-Ct-19401/unit-13/home/38330241</t>
+          <t>https://www.redfin.com/PA/Colmar/2206-Lenhart-Rd-18915/home/38363253</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>PAMC2195858</t>
+          <t>PAMC2176766</t>
         </is>
       </c>
       <c r="U73" t="n">
@@ -6729,22 +6729,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PAST SALE</t>
+          <t>MLS Listing</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Multi-Family (2-4 Unit)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2206 Lenhart Rd</t>
+          <t>618 W Lafayette St</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Colmar</t>
+          <t>Norristown</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>18915</v>
+        <v>19401</v>
       </c>
       <c r="G74" t="n">
         <v>375000</v>
@@ -6762,37 +6762,37 @@
         <v>4</v>
       </c>
       <c r="I74" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Colmar</t>
+          <t>NORRISTOWN</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>1813</v>
+        <v>2296</v>
       </c>
       <c r="L74" t="n">
-        <v>43560</v>
+        <v>11818</v>
       </c>
       <c r="M74" t="n">
-        <v>1950</v>
+        <v>1930</v>
       </c>
       <c r="N74" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O74" t="n">
-        <v>207</v>
+        <v>163</v>
       </c>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Colmar/2206-Lenhart-Rd-18915/home/38363253</t>
+          <t>https://www.redfin.com/PA/Norristown/618-W-Lafayette-St-19401/home/38108769</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>PAMC2176766</t>
+          <t>PAMC2195136</t>
         </is>
       </c>
       <c r="U74" t="n">
@@ -6815,22 +6815,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MLS Listing</t>
+          <t>PAST SALE</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Multi-Family (2-4 Unit)</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>618 W Lafayette St</t>
+          <t>204 Elm Ave</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Norristown</t>
+          <t>North Wales</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>19401</v>
+        <v>19454</v>
       </c>
       <c r="G75" t="n">
         <v>375000</v>
@@ -6852,33 +6852,33 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>NORRISTOWN</t>
+          <t>North Wales</t>
         </is>
       </c>
       <c r="K75" t="n">
-        <v>2296</v>
+        <v>1500</v>
       </c>
       <c r="L75" t="n">
-        <v>11818</v>
+        <v>7680</v>
       </c>
       <c r="M75" t="n">
-        <v>1930</v>
+        <v>1900</v>
       </c>
       <c r="N75" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="O75" t="n">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Norristown/618-W-Lafayette-St-19401/home/38108769</t>
+          <t>https://www.redfin.com/PA/North-Wales/204-Elm-Ave-19454/home/38124612</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>PAMC2195136</t>
+          <t>PAMC2188244</t>
         </is>
       </c>
       <c r="U75" t="n">
@@ -6901,22 +6901,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PAST SALE</t>
+          <t>MLS Listing</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>204 Elm Ave</t>
+          <t>1210 E Matsonford Rd</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>North Wales</t>
+          <t>Conshohocken</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6925,10 +6925,10 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>19454</v>
+        <v>19428</v>
       </c>
       <c r="G76" t="n">
-        <v>375000</v>
+        <v>379000</v>
       </c>
       <c r="H76" t="n">
         <v>4</v>
@@ -6938,33 +6938,33 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>North Wales</t>
+          <t>TATTERSALL LANE</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>1500</v>
+        <v>1638</v>
       </c>
       <c r="L76" t="n">
-        <v>7680</v>
+        <v>11425</v>
       </c>
       <c r="M76" t="n">
-        <v>1900</v>
+        <v>1950</v>
       </c>
       <c r="N76" t="n">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="O76" t="n">
-        <v>250</v>
+        <v>231</v>
       </c>
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Contingent</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/North-Wales/204-Elm-Ave-19454/home/38124612</t>
+          <t>https://www.redfin.com/PA/Conshohocken/1210-Matsonford-Rd-19428/home/38978747</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -6974,14 +6974,14 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>PAMC2188244</t>
+          <t>PAMC2188054</t>
         </is>
       </c>
       <c r="U76" t="n">
-        <v>375000</v>
+        <v>389000</v>
       </c>
       <c r="V76" t="n">
-        <v>0</v>
+        <v>-10000</v>
       </c>
     </row>
     <row r="77">
@@ -6992,17 +6992,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>1210 E Matsonford Rd</t>
+          <t>416 Calverton Ct</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Conshohocken</t>
+          <t>Harleysville</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7011,46 +7011,48 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>19428</v>
+        <v>19438</v>
       </c>
       <c r="G77" t="n">
-        <v>379000</v>
+        <v>379900</v>
       </c>
       <c r="H77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I77" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>TATTERSALL LANE</t>
+          <t>CHARLESTOWNE</t>
         </is>
       </c>
       <c r="K77" t="n">
-        <v>1638</v>
+        <v>1880</v>
       </c>
       <c r="L77" t="n">
-        <v>11425</v>
+        <v>777</v>
       </c>
       <c r="M77" t="n">
-        <v>1950</v>
+        <v>1990</v>
       </c>
       <c r="N77" t="n">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="O77" t="n">
-        <v>231</v>
-      </c>
-      <c r="P77" t="inlineStr"/>
+        <v>202</v>
+      </c>
+      <c r="P77" t="n">
+        <v>275</v>
+      </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>Contingent</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Conshohocken/1210-Matsonford-Rd-19428/home/38978747</t>
+          <t>https://www.redfin.com/PA/Harleysville/416-Calverton-Ct-19438/home/38849359</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -7060,35 +7062,31 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>PAMC2188054</t>
+          <t>PAMC2193178</t>
         </is>
       </c>
       <c r="U77" t="n">
-        <v>389000</v>
+        <v>379900</v>
       </c>
       <c r="V77" t="n">
-        <v>-10000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MLS Listing</t>
+          <t>PAST SALE</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Townhouse</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>416 Calverton Ct</t>
-        </is>
-      </c>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Harleysville</t>
+          <t>Jeffersonville</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7097,48 +7095,42 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>19438</v>
+        <v>19403</v>
       </c>
       <c r="G78" t="n">
         <v>379900</v>
       </c>
       <c r="H78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I78" t="n">
         <v>2.5</v>
       </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>CHARLESTOWNE</t>
-        </is>
-      </c>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="n">
-        <v>1880</v>
+        <v>2066</v>
       </c>
       <c r="L78" t="n">
-        <v>777</v>
+        <v>18295</v>
       </c>
       <c r="M78" t="n">
-        <v>1990</v>
+        <v>1959</v>
       </c>
       <c r="N78" t="n">
-        <v>28</v>
+        <v>310</v>
       </c>
       <c r="O78" t="n">
-        <v>202</v>
-      </c>
-      <c r="P78" t="n">
-        <v>275</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Harleysville/416-Calverton-Ct-19438/home/38849359</t>
+          <t>https://www.redfin.com/PA/Jeffersonville/Undisclosed-address-19403/home/39071152</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -7148,7 +7140,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>PAMC2193178</t>
+          <t>PAMC2161048</t>
         </is>
       </c>
       <c r="U78" t="n">
@@ -7169,10 +7161,14 @@
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr"/>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>238 Barren Hill Rd</t>
+        </is>
+      </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Jeffersonville</t>
+          <t>Conshohocken</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7181,32 +7177,36 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>19403</v>
+        <v>19428</v>
       </c>
       <c r="G79" t="n">
-        <v>379900</v>
+        <v>385000</v>
       </c>
       <c r="H79" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I79" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J79" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>SPRING MILL</t>
+        </is>
+      </c>
       <c r="K79" t="n">
-        <v>2066</v>
+        <v>1694</v>
       </c>
       <c r="L79" t="n">
-        <v>18295</v>
+        <v>4800</v>
       </c>
       <c r="M79" t="n">
-        <v>1959</v>
+        <v>1875</v>
       </c>
       <c r="N79" t="n">
-        <v>310</v>
+        <v>78</v>
       </c>
       <c r="O79" t="n">
-        <v>184</v>
+        <v>227</v>
       </c>
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Jeffersonville/Undisclosed-address-19403/home/39071152</t>
+          <t>https://www.redfin.com/PA/Conshohocken/238-Barren-Hill-Rd-19428/home/39096387</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -7226,11 +7226,11 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>PAMC2161048</t>
+          <t>PAMC2176708</t>
         </is>
       </c>
       <c r="U79" t="n">
-        <v>379900</v>
+        <v>385000</v>
       </c>
       <c r="V79" t="n">
         <v>0</v>
@@ -7239,22 +7239,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PAST SALE</t>
+          <t>MLS Listing</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>238 Barren Hill Rd</t>
+          <t>233 E Main St</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Conshohocken</t>
+          <t>Lansdale</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7263,7 +7263,7 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>19428</v>
+        <v>19446</v>
       </c>
       <c r="G80" t="n">
         <v>385000</v>
@@ -7276,33 +7276,33 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>SPRING MILL</t>
+          <t>LANSDALE</t>
         </is>
       </c>
       <c r="K80" t="n">
-        <v>1694</v>
+        <v>1916</v>
       </c>
       <c r="L80" t="n">
-        <v>4800</v>
+        <v>3300</v>
       </c>
       <c r="M80" t="n">
-        <v>1875</v>
+        <v>1925</v>
       </c>
       <c r="N80" t="n">
-        <v>78</v>
+        <v>9</v>
       </c>
       <c r="O80" t="n">
-        <v>227</v>
+        <v>201</v>
       </c>
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Conshohocken/238-Barren-Hill-Rd-19428/home/39096387</t>
+          <t>https://www.redfin.com/PA/Lansdale/233-E-Main-St-19446/home/38080309</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -7312,7 +7312,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>PAMC2176708</t>
+          <t>PAMC2193480</t>
         </is>
       </c>
       <c r="U80" t="n">
@@ -7325,17 +7325,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MLS Listing</t>
+          <t>PAST SALE</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>233 E Main St</t>
+          <t>612 S Broad St</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -7358,37 +7358,37 @@
         <v>3</v>
       </c>
       <c r="I81" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>LANSDALE</t>
+          <t>Lansdale</t>
         </is>
       </c>
       <c r="K81" t="n">
-        <v>1916</v>
+        <v>1515</v>
       </c>
       <c r="L81" t="n">
-        <v>3300</v>
+        <v>9000</v>
       </c>
       <c r="M81" t="n">
         <v>1925</v>
       </c>
       <c r="N81" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O81" t="n">
-        <v>201</v>
+        <v>254</v>
       </c>
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Lansdale/233-E-Main-St-19446/home/38080309</t>
+          <t>https://www.redfin.com/PA/Lansdale/612-S-Broad-St-19446/home/38928044</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>PAMC2193480</t>
+          <t>PAMC2193830</t>
         </is>
       </c>
       <c r="U81" t="n">
@@ -7411,22 +7411,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PAST SALE</t>
+          <t>MLS Listing</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>612 S Broad St</t>
+          <t>804 Dogwood Ln</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Lansdale</t>
+          <t>Collegeville</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7435,10 +7435,10 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>19446</v>
+        <v>19426</v>
       </c>
       <c r="G82" t="n">
-        <v>385000</v>
+        <v>389000</v>
       </c>
       <c r="H82" t="n">
         <v>3</v>
@@ -7448,33 +7448,35 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Lansdale</t>
+          <t>FAIRLAWN COURT</t>
         </is>
       </c>
       <c r="K82" t="n">
-        <v>1515</v>
+        <v>1520</v>
       </c>
       <c r="L82" t="n">
-        <v>9000</v>
+        <v>2700</v>
       </c>
       <c r="M82" t="n">
-        <v>1925</v>
+        <v>1999</v>
       </c>
       <c r="N82" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O82" t="n">
-        <v>254</v>
-      </c>
-      <c r="P82" t="inlineStr"/>
+        <v>256</v>
+      </c>
+      <c r="P82" t="n">
+        <v>50</v>
+      </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Contingent</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Lansdale/612-S-Broad-St-19446/home/38928044</t>
+          <t>https://www.redfin.com/PA/Collegeville/804-Dogwood-Ln-19426/home/39136362</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -7484,11 +7486,11 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>PAMC2193830</t>
+          <t>PAMC2191184</t>
         </is>
       </c>
       <c r="U82" t="n">
-        <v>385000</v>
+        <v>389000</v>
       </c>
       <c r="V82" t="n">
         <v>0</v>
@@ -7497,7 +7499,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MLS Listing</t>
+          <t>PAST SALE</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7507,12 +7509,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>804 Dogwood Ln</t>
+          <t>867 Main St</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Collegeville</t>
+          <t>Harleysville</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7521,10 +7523,10 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>19426</v>
+        <v>19438</v>
       </c>
       <c r="G83" t="n">
-        <v>389000</v>
+        <v>389900</v>
       </c>
       <c r="H83" t="n">
         <v>3</v>
@@ -7534,35 +7536,33 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>FAIRLAWN COURT</t>
+          <t>VERNFIELD</t>
         </is>
       </c>
       <c r="K83" t="n">
-        <v>1520</v>
+        <v>1771</v>
       </c>
       <c r="L83" t="n">
-        <v>2700</v>
+        <v>6270</v>
       </c>
       <c r="M83" t="n">
-        <v>1999</v>
+        <v>1920</v>
       </c>
       <c r="N83" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O83" t="n">
-        <v>256</v>
-      </c>
-      <c r="P83" t="n">
-        <v>50</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>Contingent</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Collegeville/804-Dogwood-Ln-19426/home/39136362</t>
+          <t>https://www.redfin.com/PA/Harleysville/867-Main-St-19438/home/38784986</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -7572,11 +7572,11 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>PAMC2191184</t>
+          <t>PAMC2194738</t>
         </is>
       </c>
       <c r="U83" t="n">
-        <v>389000</v>
+        <v>389900</v>
       </c>
       <c r="V83" t="n">
         <v>0</v>
@@ -7585,22 +7585,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>PAST SALE</t>
+          <t>MLS Listing</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Multi-Family (2-4 Unit)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>867 Main St</t>
+          <t>534 Haws Ave</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Harleysville</t>
+          <t>Norristown</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -7609,46 +7609,46 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>19438</v>
+        <v>19401</v>
       </c>
       <c r="G84" t="n">
         <v>389900</v>
       </c>
       <c r="H84" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I84" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>VERNFIELD</t>
+          <t>Norristown</t>
         </is>
       </c>
       <c r="K84" t="n">
-        <v>1771</v>
+        <v>2778</v>
       </c>
       <c r="L84" t="n">
-        <v>6270</v>
+        <v>3640</v>
       </c>
       <c r="M84" t="n">
-        <v>1920</v>
+        <v>1899</v>
       </c>
       <c r="N84" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="O84" t="n">
-        <v>220</v>
+        <v>140</v>
       </c>
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Harleysville/867-Main-St-19438/home/38784986</t>
+          <t>https://www.redfin.com/PA/Norristown/534-Haws-Ave-19401/home/38105368</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>PAMC2194738</t>
+          <t>PAMC2190620</t>
         </is>
       </c>
       <c r="U84" t="n">
@@ -7676,17 +7676,13 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Multi-Family (2-4 Unit)</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>534 Haws Ave</t>
-        </is>
-      </c>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Norristown</t>
+          <t>Willow Grove</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7695,36 +7691,32 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>19401</v>
+        <v>19090</v>
       </c>
       <c r="G85" t="n">
         <v>389900</v>
       </c>
       <c r="H85" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I85" t="n">
-        <v>2</v>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>Norristown</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="n">
-        <v>2778</v>
+        <v>1682</v>
       </c>
       <c r="L85" t="n">
-        <v>3640</v>
+        <v>9375</v>
       </c>
       <c r="M85" t="n">
-        <v>1899</v>
+        <v>1956</v>
       </c>
       <c r="N85" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="O85" t="n">
-        <v>140</v>
+        <v>232</v>
       </c>
       <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr">
@@ -7734,7 +7726,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Norristown/534-Haws-Ave-19401/home/38105368</t>
+          <t>https://www.redfin.com/PA/Willow-Grove/Undisclosed-address-19090/home/39021506</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -7744,7 +7736,7 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>PAMC2190620</t>
+          <t>PAMC2193690</t>
         </is>
       </c>
       <c r="U85" t="n">
@@ -7757,18 +7749,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MLS Listing</t>
+          <t>PAST SALE</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
+          <t>Multi-Family (2-4 Unit)</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>408 W Airy St</t>
+        </is>
+      </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Willow Grove</t>
+          <t>Norristown</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7777,42 +7773,46 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>19090</v>
+        <v>19401</v>
       </c>
       <c r="G86" t="n">
-        <v>389900</v>
+        <v>390000</v>
       </c>
       <c r="H86" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I86" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J86" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Norristown</t>
+        </is>
+      </c>
       <c r="K86" t="n">
-        <v>1682</v>
+        <v>2182</v>
       </c>
       <c r="L86" t="n">
-        <v>9375</v>
+        <v>1968</v>
       </c>
       <c r="M86" t="n">
-        <v>1956</v>
+        <v>1900</v>
       </c>
       <c r="N86" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="O86" t="n">
-        <v>232</v>
+        <v>179</v>
       </c>
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Willow-Grove/Undisclosed-address-19090/home/39021506</t>
+          <t>https://www.redfin.com/PA/Norristown/408-W-Airy-St-19401/home/38094289</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -7822,11 +7822,11 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>PAMC2193690</t>
+          <t>PAMC2176328</t>
         </is>
       </c>
       <c r="U86" t="n">
-        <v>389900</v>
+        <v>390000</v>
       </c>
       <c r="V86" t="n">
         <v>0</v>
@@ -7840,17 +7840,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Multi-Family (2-4 Unit)</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>408 W Airy St</t>
+          <t>4169 Rittenhouse Ln</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Norristown</t>
+          <t>Skippack</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -7859,38 +7859,40 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>19401</v>
+        <v>19474</v>
       </c>
       <c r="G87" t="n">
         <v>390000</v>
       </c>
       <c r="H87" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I87" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Norristown</t>
+          <t>CARRIAGE RUN</t>
         </is>
       </c>
       <c r="K87" t="n">
-        <v>2182</v>
+        <v>1520</v>
       </c>
       <c r="L87" t="n">
-        <v>1968</v>
+        <v>1600</v>
       </c>
       <c r="M87" t="n">
-        <v>1900</v>
+        <v>1983</v>
       </c>
       <c r="N87" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="O87" t="n">
-        <v>179</v>
-      </c>
-      <c r="P87" t="inlineStr"/>
+        <v>257</v>
+      </c>
+      <c r="P87" t="n">
+        <v>132</v>
+      </c>
       <c r="Q87" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -7898,7 +7900,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Norristown/408-W-Airy-St-19401/home/38094289</t>
+          <t>https://www.redfin.com/PA/Skippack/4169-Rittenhouse-Ln-19474/home/38806330</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -7908,20 +7910,20 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>PAMC2176328</t>
+          <t>PAMC2188782</t>
         </is>
       </c>
       <c r="U87" t="n">
-        <v>390000</v>
+        <v>400000</v>
       </c>
       <c r="V87" t="n">
-        <v>0</v>
+        <v>-10000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>PAST SALE</t>
+          <t>MLS Listing</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7931,12 +7933,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>4169 Rittenhouse Ln</t>
+          <t>555 Canterbury Rd</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Skippack</t>
+          <t>West Norriton</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7945,48 +7947,48 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>19474</v>
+        <v>19403</v>
       </c>
       <c r="G88" t="n">
-        <v>390000</v>
+        <v>395000</v>
       </c>
       <c r="H88" t="n">
         <v>3</v>
       </c>
       <c r="I88" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>CARRIAGE RUN</t>
+          <t>WESTOVER CROSSING</t>
         </is>
       </c>
       <c r="K88" t="n">
-        <v>1520</v>
+        <v>1530</v>
       </c>
       <c r="L88" t="n">
-        <v>1600</v>
+        <v>6850</v>
       </c>
       <c r="M88" t="n">
-        <v>1983</v>
+        <v>1985</v>
       </c>
       <c r="N88" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="O88" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P88" t="n">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Skippack/4169-Rittenhouse-Ln-19474/home/38806330</t>
+          <t>https://www.redfin.com/PA/West-Norriton/555-Canterbury-Rd-19403/home/39066897</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -7996,14 +7998,14 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>PAMC2188782</t>
+          <t>PAMC2192164</t>
         </is>
       </c>
       <c r="U88" t="n">
-        <v>400000</v>
+        <v>415000</v>
       </c>
       <c r="V88" t="n">
-        <v>-10000</v>
+        <v>-20000</v>
       </c>
     </row>
     <row r="89">
@@ -8014,17 +8016,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Multi-Family (2-4 Unit)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>555 Canterbury Rd</t>
+          <t>809 Green St</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>West Norriton</t>
+          <t>Norristown</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -8033,40 +8035,38 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>19403</v>
+        <v>19401</v>
       </c>
       <c r="G89" t="n">
         <v>395000</v>
       </c>
       <c r="H89" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I89" t="n">
         <v>2</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>WESTOVER CROSSING</t>
+          <t>Norristown</t>
         </is>
       </c>
       <c r="K89" t="n">
-        <v>1530</v>
+        <v>1992</v>
       </c>
       <c r="L89" t="n">
-        <v>6850</v>
+        <v>1440</v>
       </c>
       <c r="M89" t="n">
-        <v>1985</v>
+        <v>1885</v>
       </c>
       <c r="N89" t="n">
-        <v>38</v>
+        <v>166</v>
       </c>
       <c r="O89" t="n">
-        <v>258</v>
-      </c>
-      <c r="P89" t="n">
-        <v>110</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="P89" t="inlineStr"/>
       <c r="Q89" t="inlineStr">
         <is>
           <t>Active</t>
@@ -8074,7 +8074,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/West-Norriton/555-Canterbury-Rd-19403/home/39066897</t>
+          <t>https://www.redfin.com/PA/Norristown/809-Green-St-19401/home/38103863</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -8084,35 +8084,35 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>PAMC2192164</t>
+          <t>PAMC2176102</t>
         </is>
       </c>
       <c r="U89" t="n">
-        <v>415000</v>
+        <v>395000</v>
       </c>
       <c r="V89" t="n">
-        <v>-20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MLS Listing</t>
+          <t>PAST SALE</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Multi-Family (2-4 Unit)</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>809 Green St</t>
+          <t>139 N Main St</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Norristown</t>
+          <t>Hatfield</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -8121,46 +8121,46 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>19401</v>
+        <v>19440</v>
       </c>
       <c r="G90" t="n">
-        <v>395000</v>
+        <v>398900</v>
       </c>
       <c r="H90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Norristown</t>
+          <t>Hatfield</t>
         </is>
       </c>
       <c r="K90" t="n">
-        <v>1992</v>
+        <v>1802</v>
       </c>
       <c r="L90" t="n">
-        <v>1440</v>
+        <v>7500</v>
       </c>
       <c r="M90" t="n">
-        <v>1885</v>
+        <v>1950</v>
       </c>
       <c r="N90" t="n">
-        <v>165</v>
+        <v>19</v>
       </c>
       <c r="O90" t="n">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="P90" t="inlineStr"/>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Norristown/809-Green-St-19401/home/38103863</t>
+          <t>https://www.redfin.com/PA/Hatfield/139-N-Main-St-19440/home/38065245</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -8170,11 +8170,11 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>PAMC2176102</t>
+          <t>PAMC2186458</t>
         </is>
       </c>
       <c r="U90" t="n">
-        <v>395000</v>
+        <v>398900</v>
       </c>
       <c r="V90" t="n">
         <v>0</v>
@@ -8183,22 +8183,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PAST SALE</t>
+          <t>MLS Listing</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>139 N Main St</t>
+          <t>455 Brown Briar Cir</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Hatfield</t>
+          <t>Horsham</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8207,46 +8207,46 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>19440</v>
+        <v>19044</v>
       </c>
       <c r="G91" t="n">
-        <v>398900</v>
+        <v>399000</v>
       </c>
       <c r="H91" t="n">
         <v>3</v>
       </c>
       <c r="I91" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Hatfield</t>
+          <t>BROOKWOOD</t>
         </is>
       </c>
       <c r="K91" t="n">
-        <v>1802</v>
-      </c>
-      <c r="L91" t="n">
-        <v>7500</v>
-      </c>
+        <v>1834</v>
+      </c>
+      <c r="L91" t="inlineStr"/>
       <c r="M91" t="n">
-        <v>1950</v>
+        <v>1987</v>
       </c>
       <c r="N91" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="O91" t="n">
-        <v>221</v>
-      </c>
-      <c r="P91" t="inlineStr"/>
+        <v>218</v>
+      </c>
+      <c r="P91" t="n">
+        <v>384</v>
+      </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Hatfield/139-N-Main-St-19440/home/38065245</t>
+          <t>https://www.redfin.com/PA/Horsham/455-Brown-Briar-Cir-19044/home/38382050</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -8256,14 +8256,14 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>PAMC2186458</t>
+          <t>PAMC2193054</t>
         </is>
       </c>
       <c r="U91" t="n">
-        <v>398900</v>
+        <v>425000</v>
       </c>
       <c r="V91" t="n">
-        <v>0</v>
+        <v>-26000</v>
       </c>
     </row>
     <row r="92">
@@ -8279,12 +8279,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>455 Brown Briar Cir</t>
+          <t>1340 Markley St</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Horsham</t>
+          <t>Norristown</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -8293,7 +8293,7 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>19044</v>
+        <v>19401</v>
       </c>
       <c r="G92" t="n">
         <v>399000</v>
@@ -8306,25 +8306,25 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>BROOKWOOD</t>
+          <t>Norristown</t>
         </is>
       </c>
       <c r="K92" t="n">
-        <v>1834</v>
-      </c>
-      <c r="L92" t="inlineStr"/>
+        <v>1939</v>
+      </c>
+      <c r="L92" t="n">
+        <v>3766</v>
+      </c>
       <c r="M92" t="n">
-        <v>1987</v>
+        <v>2026</v>
       </c>
       <c r="N92" t="n">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="O92" t="n">
-        <v>218</v>
-      </c>
-      <c r="P92" t="n">
-        <v>384</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr">
         <is>
           <t>Active</t>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Horsham/455-Brown-Briar-Cir-19044/home/38382050</t>
+          <t>https://www.redfin.com/PA/Norristown/1340-Markley-St-19401/home/38109996</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -8342,14 +8342,14 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>PAMC2193054</t>
+          <t>PAMC2189340</t>
         </is>
       </c>
       <c r="U92" t="n">
-        <v>425000</v>
+        <v>424900</v>
       </c>
       <c r="V92" t="n">
-        <v>-26000</v>
+        <v>-25900</v>
       </c>
     </row>
     <row r="93">
@@ -8365,12 +8365,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>1340 Markley St</t>
+          <t>914 Dutch Dr</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Norristown</t>
+          <t>East Norriton</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8379,10 +8379,10 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>19401</v>
+        <v>19403</v>
       </c>
       <c r="G93" t="n">
-        <v>399000</v>
+        <v>399900</v>
       </c>
       <c r="H93" t="n">
         <v>3</v>
@@ -8392,25 +8392,27 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Norristown</t>
+          <t>VILLAGE OF CARALEA</t>
         </is>
       </c>
       <c r="K93" t="n">
-        <v>1939</v>
+        <v>1645</v>
       </c>
       <c r="L93" t="n">
-        <v>3766</v>
+        <v>1200</v>
       </c>
       <c r="M93" t="n">
-        <v>2026</v>
+        <v>2011</v>
       </c>
       <c r="N93" t="n">
-        <v>66</v>
+        <v>7</v>
       </c>
       <c r="O93" t="n">
-        <v>206</v>
-      </c>
-      <c r="P93" t="inlineStr"/>
+        <v>243</v>
+      </c>
+      <c r="P93" t="n">
+        <v>178</v>
+      </c>
       <c r="Q93" t="inlineStr">
         <is>
           <t>Active</t>
@@ -8418,7 +8420,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Norristown/1340-Markley-St-19401/home/38109996</t>
+          <t>https://www.redfin.com/PA/East-Norriton/914-Dutch-Dr-19403/home/38022886</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -8428,20 +8430,20 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>PAMC2189340</t>
+          <t>PAMC2195168</t>
         </is>
       </c>
       <c r="U93" t="n">
-        <v>424900</v>
+        <v>399900</v>
       </c>
       <c r="V93" t="n">
-        <v>-25900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MLS Listing</t>
+          <t>PAST SALE</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8451,12 +8453,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>914 Dutch Dr</t>
+          <t>818 N Chestnut St</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>East Norriton</t>
+          <t>Lansdale</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8465,7 +8467,7 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>19403</v>
+        <v>19446</v>
       </c>
       <c r="G94" t="n">
         <v>399900</v>
@@ -8474,39 +8476,37 @@
         <v>3</v>
       </c>
       <c r="I94" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>VILLAGE OF CARALEA</t>
+          <t>Lansdale</t>
         </is>
       </c>
       <c r="K94" t="n">
-        <v>1645</v>
+        <v>1504</v>
       </c>
       <c r="L94" t="n">
-        <v>1200</v>
+        <v>5480</v>
       </c>
       <c r="M94" t="n">
-        <v>2011</v>
+        <v>1926</v>
       </c>
       <c r="N94" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O94" t="n">
-        <v>243</v>
-      </c>
-      <c r="P94" t="n">
-        <v>178</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/East-Norriton/914-Dutch-Dr-19403/home/38022886</t>
+          <t>https://www.redfin.com/PA/Lansdale/818-N-Chestnut-St-19446/home/38074710</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>PAMC2195168</t>
+          <t>PAMC2185718</t>
         </is>
       </c>
       <c r="U94" t="n">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>818 N Chestnut St</t>
+          <t>342 Perkiomen Ave</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -8559,10 +8559,10 @@
         <v>399900</v>
       </c>
       <c r="H95" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I95" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -8570,19 +8570,19 @@
         </is>
       </c>
       <c r="K95" t="n">
-        <v>1504</v>
+        <v>2814</v>
       </c>
       <c r="L95" t="n">
-        <v>5480</v>
+        <v>9750</v>
       </c>
       <c r="M95" t="n">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="N95" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="O95" t="n">
-        <v>266</v>
+        <v>142</v>
       </c>
       <c r="P95" t="inlineStr"/>
       <c r="Q95" t="inlineStr">
@@ -8592,7 +8592,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Lansdale/818-N-Chestnut-St-19446/home/38074710</t>
+          <t>https://www.redfin.com/PA/Lansdale/342-Perkiomen-Ave-19446/home/38084545</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -8602,7 +8602,7 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>PAMC2185718</t>
+          <t>PAMC2177110</t>
         </is>
       </c>
       <c r="U95" t="n">
@@ -8615,22 +8615,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PAST SALE</t>
+          <t>MLS Listing</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>342 Perkiomen Ave</t>
+          <t>33 Centre Ave</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Lansdale</t>
+          <t>West Norriton</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -8639,46 +8639,46 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>19446</v>
+        <v>19403</v>
       </c>
       <c r="G96" t="n">
-        <v>399900</v>
+        <v>399999</v>
       </c>
       <c r="H96" t="n">
         <v>4</v>
       </c>
       <c r="I96" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Lansdale</t>
+          <t>CENTRE AVE CONDOS</t>
         </is>
       </c>
       <c r="K96" t="n">
-        <v>2814</v>
+        <v>1578</v>
       </c>
       <c r="L96" t="n">
-        <v>9750</v>
+        <v>5200</v>
       </c>
       <c r="M96" t="n">
         <v>1930</v>
       </c>
       <c r="N96" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="O96" t="n">
-        <v>142</v>
+        <v>253</v>
       </c>
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Lansdale/342-Perkiomen-Ave-19446/home/38084545</t>
+          <t>https://www.redfin.com/PA/West-Norriton/33-Centre-Ave-19403/home/39067056</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -8688,11 +8688,11 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>PAMC2177110</t>
+          <t>PAMC2190854</t>
         </is>
       </c>
       <c r="U96" t="n">
-        <v>399900</v>
+        <v>399999</v>
       </c>
       <c r="V96" t="n">
         <v>0</v>
@@ -8711,12 +8711,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>33 Centre Ave</t>
+          <t>10 W Township Line Rd</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>West Norriton</t>
+          <t>East Norriton</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -8725,10 +8725,10 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>19403</v>
+        <v>19401</v>
       </c>
       <c r="G97" t="n">
-        <v>399999</v>
+        <v>400000</v>
       </c>
       <c r="H97" t="n">
         <v>4</v>
@@ -8738,23 +8738,23 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>CENTRE AVE CONDOS</t>
+          <t>NORRISTOWN</t>
         </is>
       </c>
       <c r="K97" t="n">
-        <v>1578</v>
+        <v>1972</v>
       </c>
       <c r="L97" t="n">
-        <v>5200</v>
+        <v>14686</v>
       </c>
       <c r="M97" t="n">
-        <v>1930</v>
+        <v>1900</v>
       </c>
       <c r="N97" t="n">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="O97" t="n">
-        <v>253</v>
+        <v>203</v>
       </c>
       <c r="P97" t="inlineStr"/>
       <c r="Q97" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/West-Norriton/33-Centre-Ave-19403/home/39067056</t>
+          <t>https://www.redfin.com/PA/East-Norriton/10-W-Township-Line-Rd-19401/home/38336640</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -8774,11 +8774,11 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>PAMC2190854</t>
+          <t>PAMC2188352</t>
         </is>
       </c>
       <c r="U97" t="n">
-        <v>399999</v>
+        <v>400000</v>
       </c>
       <c r="V97" t="n">
         <v>0</v>
@@ -8787,22 +8787,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MLS Listing</t>
+          <t>PAST SALE</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>10 W Township Line Rd</t>
+          <t>4 Loggers Mill Rd</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>East Norriton</t>
+          <t>Horsham</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8811,46 +8811,46 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>19401</v>
+        <v>19044</v>
       </c>
       <c r="G98" t="n">
         <v>400000</v>
       </c>
       <c r="H98" t="n">
+        <v>3</v>
+      </c>
+      <c r="I98" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>SAW MILL VALLEY</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>1854</v>
+      </c>
+      <c r="L98" t="n">
+        <v>3694</v>
+      </c>
+      <c r="M98" t="n">
+        <v>1982</v>
+      </c>
+      <c r="N98" t="n">
         <v>4</v>
       </c>
-      <c r="I98" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>NORRISTOWN</t>
-        </is>
-      </c>
-      <c r="K98" t="n">
-        <v>1972</v>
-      </c>
-      <c r="L98" t="n">
-        <v>14686</v>
-      </c>
-      <c r="M98" t="n">
-        <v>1900</v>
-      </c>
-      <c r="N98" t="n">
-        <v>9</v>
-      </c>
       <c r="O98" t="n">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="P98" t="inlineStr"/>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/East-Norriton/10-W-Township-Line-Rd-19401/home/38336640</t>
+          <t>https://www.redfin.com/PA/Horsham/4-Loggers-Mill-Rd-19044/home/38401639</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -8860,7 +8860,7 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>PAMC2188352</t>
+          <t>PAMC2194660</t>
         </is>
       </c>
       <c r="U98" t="n">
@@ -8878,17 +8878,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>4 Loggers Mill Rd</t>
+          <t>370 Hillside Rd</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Horsham</t>
+          <t>King Of Prussia</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8897,7 +8897,7 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>19044</v>
+        <v>19406</v>
       </c>
       <c r="G99" t="n">
         <v>400000</v>
@@ -8906,27 +8906,27 @@
         <v>3</v>
       </c>
       <c r="I99" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>SAW MILL VALLEY</t>
+          <t>VALLEY FORGE ACRES</t>
         </is>
       </c>
       <c r="K99" t="n">
-        <v>1854</v>
+        <v>1761</v>
       </c>
       <c r="L99" t="n">
-        <v>3694</v>
+        <v>10019</v>
       </c>
       <c r="M99" t="n">
-        <v>1982</v>
+        <v>1959</v>
       </c>
       <c r="N99" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="O99" t="n">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="P99" t="inlineStr"/>
       <c r="Q99" t="inlineStr">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Horsham/4-Loggers-Mill-Rd-19044/home/38401639</t>
+          <t>https://www.redfin.com/PA/King-of-Prussia/370-Hillside-Rd-19406/home/38972684</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
@@ -8946,35 +8946,35 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>PAMC2194660</t>
+          <t>PAMC2191738</t>
         </is>
       </c>
       <c r="U99" t="n">
-        <v>400000</v>
+        <v>515000</v>
       </c>
       <c r="V99" t="n">
-        <v>0</v>
+        <v>-115000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PAST SALE</t>
+          <t>MLS Listing</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Multi-Family (2-4 Unit)</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>370 Hillside Rd</t>
+          <t>1009 Dekalb St</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>King Of Prussia</t>
+          <t>Norristown</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8983,46 +8983,46 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>19406</v>
+        <v>19401</v>
       </c>
       <c r="G100" t="n">
         <v>400000</v>
       </c>
       <c r="H100" t="n">
+        <v>5</v>
+      </c>
+      <c r="I100" t="n">
         <v>3</v>
       </c>
-      <c r="I100" t="n">
-        <v>2</v>
-      </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>VALLEY FORGE ACRES</t>
+          <t>NORRISTOWN</t>
         </is>
       </c>
       <c r="K100" t="n">
-        <v>1761</v>
+        <v>3352</v>
       </c>
       <c r="L100" t="n">
-        <v>10019</v>
+        <v>5460</v>
       </c>
       <c r="M100" t="n">
-        <v>1959</v>
+        <v>1900</v>
       </c>
       <c r="N100" t="n">
-        <v>34</v>
+        <v>422</v>
       </c>
       <c r="O100" t="n">
-        <v>227</v>
+        <v>119</v>
       </c>
       <c r="P100" t="inlineStr"/>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/King-of-Prussia/370-Hillside-Rd-19406/home/38972684</t>
+          <t>https://www.redfin.com/PA/Norristown/1009-DeKalb-St-19401/home/38100727</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -9032,14 +9032,14 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>PAMC2191738</t>
+          <t>PAMC2150636</t>
         </is>
       </c>
       <c r="U100" t="n">
-        <v>515000</v>
+        <v>400000</v>
       </c>
       <c r="V100" t="n">
-        <v>-115000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -9050,17 +9050,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Multi-Family (2-4 Unit)</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>1009 Dekalb St</t>
+          <t>58 N School Ln</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Norristown</t>
+          <t>Souderton</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -9069,38 +9069,40 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>19401</v>
+        <v>18964</v>
       </c>
       <c r="G101" t="n">
         <v>400000</v>
       </c>
       <c r="H101" t="n">
+        <v>3</v>
+      </c>
+      <c r="I101" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>BERKELEY COURT</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>1826</v>
+      </c>
+      <c r="L101" t="n">
+        <v>1874</v>
+      </c>
+      <c r="M101" t="n">
+        <v>2014</v>
+      </c>
+      <c r="N101" t="n">
         <v>5</v>
       </c>
-      <c r="I101" t="n">
-        <v>3</v>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>NORRISTOWN</t>
-        </is>
-      </c>
-      <c r="K101" t="n">
-        <v>3352</v>
-      </c>
-      <c r="L101" t="n">
-        <v>5460</v>
-      </c>
-      <c r="M101" t="n">
-        <v>1900</v>
-      </c>
-      <c r="N101" t="n">
-        <v>421</v>
-      </c>
       <c r="O101" t="n">
-        <v>119</v>
-      </c>
-      <c r="P101" t="inlineStr"/>
+        <v>219</v>
+      </c>
+      <c r="P101" t="n">
+        <v>261</v>
+      </c>
       <c r="Q101" t="inlineStr">
         <is>
           <t>Active</t>
@@ -9108,7 +9110,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Norristown/1009-DeKalb-St-19401/home/38100727</t>
+          <t>https://www.redfin.com/PA/Souderton/58-N-School-Ln-18964/home/69097468</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -9118,7 +9120,7 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>PAMC2150636</t>
+          <t>PAMC2195508</t>
         </is>
       </c>
       <c r="U101" t="n">
@@ -9131,7 +9133,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MLS Listing</t>
+          <t>PAST SALE</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9141,12 +9143,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>58 N School Ln</t>
+          <t>3296 Roxbury Rd</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Souderton</t>
+          <t>Hatfield</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -9155,48 +9157,44 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>18964</v>
+        <v>19440</v>
       </c>
       <c r="G102" t="n">
-        <v>400000</v>
+        <v>410000</v>
       </c>
       <c r="H102" t="n">
         <v>3</v>
       </c>
       <c r="I102" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>BERKELEY COURT</t>
+          <t>LEXINGTON FARMS</t>
         </is>
       </c>
       <c r="K102" t="n">
-        <v>1826</v>
+        <v>1672</v>
       </c>
       <c r="L102" t="n">
-        <v>1874</v>
+        <v>12384</v>
       </c>
       <c r="M102" t="n">
-        <v>2014</v>
-      </c>
-      <c r="N102" t="n">
-        <v>4</v>
-      </c>
+        <v>1985</v>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="O102" t="n">
-        <v>219</v>
-      </c>
-      <c r="P102" t="n">
-        <v>261</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="P102" t="inlineStr"/>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Souderton/58-N-School-Ln-18964/home/69097468</t>
+          <t>https://www.redfin.com/PA/Hatfield/3296-Roxbury-Rd-19440/home/38370754</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -9206,11 +9204,11 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>PAMC2195508</t>
+          <t>PAMC2188480</t>
         </is>
       </c>
       <c r="U102" t="n">
-        <v>400000</v>
+        <v>410000</v>
       </c>
       <c r="V102" t="n">
         <v>0</v>
@@ -9219,7 +9217,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>PAST SALE</t>
+          <t>MLS Listing</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9229,12 +9227,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>3296 Roxbury Rd</t>
+          <t>89 Queens Cir</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Hatfield</t>
+          <t>Chalfont</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -9243,10 +9241,10 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>19440</v>
+        <v>18914</v>
       </c>
       <c r="G103" t="n">
-        <v>410000</v>
+        <v>415000</v>
       </c>
       <c r="H103" t="n">
         <v>3</v>
@@ -9256,31 +9254,35 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>LEXINGTON FARMS</t>
+          <t>THE HIGHLANDS</t>
         </is>
       </c>
       <c r="K103" t="n">
-        <v>1672</v>
+        <v>1555</v>
       </c>
       <c r="L103" t="n">
-        <v>12384</v>
+        <v>2310</v>
       </c>
       <c r="M103" t="n">
-        <v>1985</v>
-      </c>
-      <c r="N103" t="inlineStr"/>
+        <v>1977</v>
+      </c>
+      <c r="N103" t="n">
+        <v>3</v>
+      </c>
       <c r="O103" t="n">
-        <v>245</v>
-      </c>
-      <c r="P103" t="inlineStr"/>
+        <v>267</v>
+      </c>
+      <c r="P103" t="n">
+        <v>180</v>
+      </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Hatfield/3296-Roxbury-Rd-19440/home/38370754</t>
+          <t>https://www.redfin.com/PA/Chalfont/89-Queens-Cir-18914/home/38919192</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
@@ -9290,11 +9292,11 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>PAMC2188480</t>
+          <t>PABU2132300</t>
         </is>
       </c>
       <c r="U103" t="n">
-        <v>410000</v>
+        <v>415000</v>
       </c>
       <c r="V103" t="n">
         <v>0</v>
@@ -9313,12 +9315,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>89 Queens Cir</t>
+          <t>385 Hamilton Dr</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Chalfont</t>
+          <t>Harleysville</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -9327,7 +9329,7 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>18914</v>
+        <v>19438</v>
       </c>
       <c r="G104" t="n">
         <v>415000</v>
@@ -9336,39 +9338,39 @@
         <v>3</v>
       </c>
       <c r="I104" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>THE HIGHLANDS</t>
+          <t>ROSECLIFF MANOR</t>
         </is>
       </c>
       <c r="K104" t="n">
-        <v>1555</v>
+        <v>1642</v>
       </c>
       <c r="L104" t="n">
-        <v>2310</v>
+        <v>1650</v>
       </c>
       <c r="M104" t="n">
-        <v>1977</v>
+        <v>1998</v>
       </c>
       <c r="N104" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="O104" t="n">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="P104" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Contingent</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Chalfont/89-Queens-Cir-18914/home/38919192</t>
+          <t>https://www.redfin.com/PA/Harleysville/385-Hamilton-Dr-19438/home/38781804</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
@@ -9378,7 +9380,7 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>PABU2132300</t>
+          <t>PAMC2192608</t>
         </is>
       </c>
       <c r="U104" t="n">
@@ -9401,12 +9403,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>385 Hamilton Dr</t>
+          <t>418 Jefferson St</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Harleysville</t>
+          <t>Lansdale</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -9415,7 +9417,7 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>19438</v>
+        <v>19446</v>
       </c>
       <c r="G105" t="n">
         <v>415000</v>
@@ -9424,39 +9426,37 @@
         <v>3</v>
       </c>
       <c r="I105" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>ROSECLIFF MANOR</t>
+          <t>Lansdale</t>
         </is>
       </c>
       <c r="K105" t="n">
-        <v>1642</v>
+        <v>2000</v>
       </c>
       <c r="L105" t="n">
-        <v>1650</v>
+        <v>3920</v>
       </c>
       <c r="M105" t="n">
-        <v>1998</v>
+        <v>1961</v>
       </c>
       <c r="N105" t="n">
-        <v>19</v>
+        <v>158</v>
       </c>
       <c r="O105" t="n">
-        <v>253</v>
-      </c>
-      <c r="P105" t="n">
-        <v>160</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="P105" t="inlineStr"/>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>Contingent</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Harleysville/385-Hamilton-Dr-19438/home/38781804</t>
+          <t>https://www.redfin.com/PA/Lansdale/418-Jefferson-St-19446/home/38080453</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>PAMC2192608</t>
+          <t>PAMC2176534</t>
         </is>
       </c>
       <c r="U105" t="n">
@@ -9484,17 +9484,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>418 Jefferson St</t>
+          <t>515 Hamilton St</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Lansdale</t>
+          <t>Norristown</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -9503,46 +9503,46 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>19446</v>
+        <v>19401</v>
       </c>
       <c r="G106" t="n">
         <v>415000</v>
       </c>
       <c r="H106" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I106" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Lansdale</t>
+          <t>NORRISTOWN</t>
         </is>
       </c>
       <c r="K106" t="n">
-        <v>2000</v>
+        <v>3388</v>
       </c>
       <c r="L106" t="n">
-        <v>3920</v>
+        <v>9100</v>
       </c>
       <c r="M106" t="n">
-        <v>1961</v>
+        <v>1924</v>
       </c>
       <c r="N106" t="n">
-        <v>157</v>
+        <v>5</v>
       </c>
       <c r="O106" t="n">
-        <v>208</v>
+        <v>122</v>
       </c>
       <c r="P106" t="inlineStr"/>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Contingent</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Lansdale/418-Jefferson-St-19446/home/38080453</t>
+          <t>https://www.redfin.com/PA/Norristown/515-Hamilton-St-19401/home/38105216</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
@@ -9552,7 +9552,7 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>PAMC2176534</t>
+          <t>PAMC2194464</t>
         </is>
       </c>
       <c r="U106" t="n">
@@ -9570,17 +9570,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>515 Hamilton St</t>
+          <t>97 Palace Ct</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Norristown</t>
+          <t>Chalfont</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -9589,46 +9589,46 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>19401</v>
+        <v>18914</v>
       </c>
       <c r="G107" t="n">
-        <v>415000</v>
+        <v>424000</v>
       </c>
       <c r="H107" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I107" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>NORRISTOWN</t>
+          <t>THE HIGHLANDS</t>
         </is>
       </c>
       <c r="K107" t="n">
-        <v>3388</v>
-      </c>
-      <c r="L107" t="n">
-        <v>9100</v>
-      </c>
+        <v>1756</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
       <c r="M107" t="n">
-        <v>1924</v>
+        <v>1982</v>
       </c>
       <c r="N107" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="O107" t="n">
-        <v>122</v>
-      </c>
-      <c r="P107" t="inlineStr"/>
+        <v>241</v>
+      </c>
+      <c r="P107" t="n">
+        <v>180</v>
+      </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>Contingent</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Norristown/515-Hamilton-St-19401/home/38105216</t>
+          <t>https://www.redfin.com/PA/Chalfont/97-Palace-Ct-18914/home/38921114</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
@@ -9638,11 +9638,11 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>PAMC2194464</t>
+          <t>PABU2130576</t>
         </is>
       </c>
       <c r="U107" t="n">
-        <v>415000</v>
+        <v>424000</v>
       </c>
       <c r="V107" t="n">
         <v>0</v>
@@ -9661,12 +9661,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>97 Palace Ct</t>
+          <t>1342 Markley St</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Chalfont</t>
+          <t>Norristown</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -9675,38 +9675,38 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>18914</v>
+        <v>19401</v>
       </c>
       <c r="G108" t="n">
-        <v>424000</v>
+        <v>424900</v>
       </c>
       <c r="H108" t="n">
         <v>3</v>
       </c>
       <c r="I108" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>THE HIGHLANDS</t>
+          <t>Norristown</t>
         </is>
       </c>
       <c r="K108" t="n">
-        <v>1756</v>
-      </c>
-      <c r="L108" t="inlineStr"/>
+        <v>1939</v>
+      </c>
+      <c r="L108" t="n">
+        <v>3931</v>
+      </c>
       <c r="M108" t="n">
-        <v>1982</v>
+        <v>2026</v>
       </c>
       <c r="N108" t="n">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="O108" t="n">
-        <v>241</v>
-      </c>
-      <c r="P108" t="n">
-        <v>180</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="P108" t="inlineStr"/>
       <c r="Q108" t="inlineStr">
         <is>
           <t>Active</t>
@@ -9714,7 +9714,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Chalfont/97-Palace-Ct-18914/home/38921114</t>
+          <t>https://www.redfin.com/PA/Norristown/1342-Markley-St-19401/home/40524749</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -9724,11 +9724,11 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>PABU2130576</t>
+          <t>PAMC2189294</t>
         </is>
       </c>
       <c r="U108" t="n">
-        <v>424000</v>
+        <v>424900</v>
       </c>
       <c r="V108" t="n">
         <v>0</v>
@@ -9747,12 +9747,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>1342 Markley St</t>
+          <t>102 Poplar Ct</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Norristown</t>
+          <t>Collegeville</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -9761,10 +9761,10 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>19401</v>
+        <v>19426</v>
       </c>
       <c r="G109" t="n">
-        <v>424900</v>
+        <v>425000</v>
       </c>
       <c r="H109" t="n">
         <v>3</v>
@@ -9774,25 +9774,27 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Norristown</t>
+          <t>PERKIOMEN WOODS</t>
         </is>
       </c>
       <c r="K109" t="n">
-        <v>1939</v>
+        <v>1798</v>
       </c>
       <c r="L109" t="n">
-        <v>3931</v>
+        <v>1999</v>
       </c>
       <c r="M109" t="n">
-        <v>2026</v>
+        <v>1994</v>
       </c>
       <c r="N109" t="n">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="O109" t="n">
-        <v>219</v>
-      </c>
-      <c r="P109" t="inlineStr"/>
+        <v>236</v>
+      </c>
+      <c r="P109" t="n">
+        <v>150</v>
+      </c>
       <c r="Q109" t="inlineStr">
         <is>
           <t>Active</t>
@@ -9800,7 +9802,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Norristown/1342-Markley-St-19401/home/40524749</t>
+          <t>https://www.redfin.com/PA/Collegeville/102-Poplar-Ct-19426/home/39051024</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
@@ -9810,11 +9812,11 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>PAMC2189294</t>
+          <t>PAMC2194576</t>
         </is>
       </c>
       <c r="U109" t="n">
-        <v>424900</v>
+        <v>425000</v>
       </c>
       <c r="V109" t="n">
         <v>0</v>
@@ -9823,22 +9825,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>MLS Listing</t>
+          <t>PAST SALE</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>102 Poplar Ct</t>
+          <t>51 Belmont Sq</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Collegeville</t>
+          <t>Doylestown</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -9847,7 +9849,7 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>19426</v>
+        <v>18901</v>
       </c>
       <c r="G110" t="n">
         <v>425000</v>
@@ -9860,35 +9862,33 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>PERKIOMEN WOODS</t>
+          <t>FAIRVIEW</t>
         </is>
       </c>
       <c r="K110" t="n">
-        <v>1798</v>
+        <v>1874</v>
       </c>
       <c r="L110" t="n">
-        <v>1999</v>
+        <v>7405</v>
       </c>
       <c r="M110" t="n">
-        <v>1994</v>
+        <v>1971</v>
       </c>
       <c r="N110" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="O110" t="n">
-        <v>236</v>
-      </c>
-      <c r="P110" t="n">
-        <v>150</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="P110" t="inlineStr"/>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Collegeville/102-Poplar-Ct-19426/home/39051024</t>
+          <t>https://www.redfin.com/PA/Doylestown/51-Belmont-Sq-18901/home/38576386</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
@@ -9898,7 +9898,7 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>PAMC2194576</t>
+          <t>PABU2132310</t>
         </is>
       </c>
       <c r="U110" t="n">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>51 Belmont Sq</t>
+          <t>325 E Mount Kirk Ave</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Doylestown</t>
+          <t>Norristown</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -9935,7 +9935,7 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>18901</v>
+        <v>19403</v>
       </c>
       <c r="G111" t="n">
         <v>425000</v>
@@ -9944,27 +9944,27 @@
         <v>3</v>
       </c>
       <c r="I111" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>FAIRVIEW</t>
+          <t>Eagleville</t>
         </is>
       </c>
       <c r="K111" t="n">
-        <v>1874</v>
+        <v>2204</v>
       </c>
       <c r="L111" t="n">
-        <v>7405</v>
+        <v>34000</v>
       </c>
       <c r="M111" t="n">
-        <v>1971</v>
+        <v>1958</v>
       </c>
       <c r="N111" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O111" t="n">
-        <v>227</v>
+        <v>193</v>
       </c>
       <c r="P111" t="inlineStr"/>
       <c r="Q111" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Doylestown/51-Belmont-Sq-18901/home/38576386</t>
+          <t>https://www.redfin.com/PA/Norristown/325-E-Mount-Kirk-Ave-19403/home/39127827</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>PABU2132310</t>
+          <t>PAMC2195930</t>
         </is>
       </c>
       <c r="U111" t="n">
@@ -10002,12 +10002,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>325 E Mount Kirk Ave</t>
+          <t>43 Hampton Ct</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -10030,29 +10030,31 @@
         <v>3</v>
       </c>
       <c r="I112" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Eagleville</t>
+          <t>BERWICK PL</t>
         </is>
       </c>
       <c r="K112" t="n">
-        <v>2204</v>
+        <v>2016</v>
       </c>
       <c r="L112" t="n">
-        <v>34000</v>
+        <v>1200</v>
       </c>
       <c r="M112" t="n">
-        <v>1958</v>
+        <v>1994</v>
       </c>
       <c r="N112" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="O112" t="n">
-        <v>193</v>
-      </c>
-      <c r="P112" t="inlineStr"/>
+        <v>211</v>
+      </c>
+      <c r="P112" t="n">
+        <v>250</v>
+      </c>
       <c r="Q112" t="inlineStr">
         <is>
           <t>Active</t>
@@ -10060,7 +10062,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Norristown/325-E-Mount-Kirk-Ave-19403/home/39127827</t>
+          <t>https://www.redfin.com/PA/Norristown/43-Hampton-Ct-19403/home/39127523</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
@@ -10070,14 +10072,14 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>PAMC2195930</t>
+          <t>PAMC2186450</t>
         </is>
       </c>
       <c r="U112" t="n">
-        <v>425000</v>
+        <v>422900</v>
       </c>
       <c r="V112" t="n">
-        <v>0</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="113">
@@ -10088,12 +10090,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Multi-Family (2-4 Unit)</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>43 Hampton Ct</t>
+          <t>112 Haws Ave</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -10107,40 +10109,38 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>19403</v>
+        <v>19401</v>
       </c>
       <c r="G113" t="n">
         <v>425000</v>
       </c>
       <c r="H113" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I113" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>BERWICK PL</t>
+          <t>Norristown</t>
         </is>
       </c>
       <c r="K113" t="n">
-        <v>2016</v>
+        <v>2374</v>
       </c>
       <c r="L113" t="n">
-        <v>1200</v>
+        <v>4496</v>
       </c>
       <c r="M113" t="n">
-        <v>1994</v>
+        <v>1930</v>
       </c>
       <c r="N113" t="n">
-        <v>36</v>
+        <v>166</v>
       </c>
       <c r="O113" t="n">
-        <v>211</v>
-      </c>
-      <c r="P113" t="n">
-        <v>250</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="P113" t="inlineStr"/>
       <c r="Q113" t="inlineStr">
         <is>
           <t>Active</t>
@@ -10148,7 +10148,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Norristown/43-Hampton-Ct-19403/home/39127523</t>
+          <t>https://www.redfin.com/PA/Norristown/112-Haws-Ave-19401/home/38105473</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
@@ -10158,30 +10158,30 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>PAMC2186450</t>
+          <t>PAMC2176196</t>
         </is>
       </c>
       <c r="U113" t="n">
-        <v>422900</v>
+        <v>425000</v>
       </c>
       <c r="V113" t="n">
-        <v>2100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MLS Listing</t>
+          <t>PAST SALE</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Multi-Family (2-4 Unit)</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>112 Haws Ave</t>
+          <t>405 Sweet Bay Ln</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -10195,46 +10195,48 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>19401</v>
+        <v>19403</v>
       </c>
       <c r="G114" t="n">
         <v>425000</v>
       </c>
       <c r="H114" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I114" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>RESERVE AT STONY CREEK</t>
+        </is>
+      </c>
+      <c r="K114" t="n">
+        <v>1881</v>
+      </c>
+      <c r="L114" t="n">
+        <v>1089</v>
+      </c>
+      <c r="M114" t="n">
+        <v>2023</v>
+      </c>
+      <c r="N114" t="n">
         <v>2</v>
       </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>Norristown</t>
-        </is>
-      </c>
-      <c r="K114" t="n">
-        <v>2374</v>
-      </c>
-      <c r="L114" t="n">
-        <v>4496</v>
-      </c>
-      <c r="M114" t="n">
-        <v>1930</v>
-      </c>
-      <c r="N114" t="n">
-        <v>165</v>
-      </c>
       <c r="O114" t="n">
-        <v>179</v>
-      </c>
-      <c r="P114" t="inlineStr"/>
+        <v>226</v>
+      </c>
+      <c r="P114" t="n">
+        <v>208</v>
+      </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Norristown/112-Haws-Ave-19401/home/38105473</t>
+          <t>https://www.redfin.com/PA/Norristown/405-Sweet-Bay-Ln-19403/home/190260791</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
@@ -10244,7 +10246,7 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>PAMC2176196</t>
+          <t>PAMC2188062</t>
         </is>
       </c>
       <c r="U114" t="n">
@@ -10262,17 +10264,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>405 Sweet Bay Ln</t>
+          <t>157 Egypt Rd</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Norristown</t>
+          <t>West Norriton</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -10290,31 +10292,29 @@
         <v>3</v>
       </c>
       <c r="I115" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>RESERVE AT STONY CREEK</t>
+          <t>JEFFERSONVILLE</t>
         </is>
       </c>
       <c r="K115" t="n">
-        <v>1881</v>
+        <v>1524</v>
       </c>
       <c r="L115" t="n">
-        <v>1089</v>
+        <v>28000</v>
       </c>
       <c r="M115" t="n">
-        <v>2023</v>
+        <v>1956</v>
       </c>
       <c r="N115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O115" t="n">
-        <v>226</v>
-      </c>
-      <c r="P115" t="n">
-        <v>208</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="P115" t="inlineStr"/>
       <c r="Q115" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -10322,7 +10322,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Norristown/405-Sweet-Bay-Ln-19403/home/190260791</t>
+          <t>https://www.redfin.com/PA/West-Norriton/157-Egypt-Rd-19403/home/39068971</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
@@ -10332,7 +10332,7 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>PAMC2188062</t>
+          <t>PAMC2194282</t>
         </is>
       </c>
       <c r="U115" t="n">
@@ -10355,7 +10355,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>157 Egypt Rd</t>
+          <t>53 Crawford</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -10378,27 +10378,27 @@
         <v>3</v>
       </c>
       <c r="I116" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>JEFFERSONVILLE</t>
+          <t>West Norriton</t>
         </is>
       </c>
       <c r="K116" t="n">
-        <v>1524</v>
+        <v>1507</v>
       </c>
       <c r="L116" t="n">
-        <v>28000</v>
+        <v>13800</v>
       </c>
       <c r="M116" t="n">
-        <v>1956</v>
+        <v>1954</v>
       </c>
       <c r="N116" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O116" t="n">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="P116" t="inlineStr"/>
       <c r="Q116" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/West-Norriton/157-Egypt-Rd-19403/home/39068971</t>
+          <t>https://www.redfin.com/PA/West-Norriton/53-Crawford-Dr-19403/home/39069177</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
@@ -10418,14 +10418,14 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>PAMC2194282</t>
+          <t>PAMC2193880</t>
         </is>
       </c>
       <c r="U116" t="n">
-        <v>425000</v>
+        <v>435000</v>
       </c>
       <c r="V116" t="n">
-        <v>0</v>
+        <v>-10000</v>
       </c>
     </row>
     <row r="117">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>53 Crawford</t>
+          <t>124 Church Rd</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>West Norriton</t>
+          <t>North Wales</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -10455,7 +10455,7 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>19403</v>
+        <v>19454</v>
       </c>
       <c r="G117" t="n">
         <v>425000</v>
@@ -10464,27 +10464,27 @@
         <v>3</v>
       </c>
       <c r="I117" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>West Norriton</t>
+          <t>North Wales</t>
         </is>
       </c>
       <c r="K117" t="n">
-        <v>1507</v>
+        <v>1736</v>
       </c>
       <c r="L117" t="n">
-        <v>13800</v>
+        <v>15552</v>
       </c>
       <c r="M117" t="n">
-        <v>1954</v>
+        <v>1952</v>
       </c>
       <c r="N117" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O117" t="n">
-        <v>282</v>
+        <v>245</v>
       </c>
       <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr">
@@ -10494,7 +10494,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/West-Norriton/53-Crawford-Dr-19403/home/39069177</t>
+          <t>https://www.redfin.com/PA/North-Wales/124-Church-Rd-19454/home/38930705</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
@@ -10504,35 +10504,35 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>PAMC2193880</t>
+          <t>PAMC2192188</t>
         </is>
       </c>
       <c r="U117" t="n">
-        <v>435000</v>
+        <v>425000</v>
       </c>
       <c r="V117" t="n">
-        <v>-10000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>PAST SALE</t>
+          <t>MLS Listing</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>124 Church Rd</t>
+          <t>315--A Olive Ave</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>North Wales</t>
+          <t>Horsham</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -10541,10 +10541,10 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>19454</v>
+        <v>19044</v>
       </c>
       <c r="G118" t="n">
-        <v>425000</v>
+        <v>429000</v>
       </c>
       <c r="H118" t="n">
         <v>3</v>
@@ -10554,33 +10554,33 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>North Wales</t>
+          <t>Horsham</t>
         </is>
       </c>
       <c r="K118" t="n">
-        <v>1736</v>
+        <v>1620</v>
       </c>
       <c r="L118" t="n">
-        <v>15552</v>
+        <v>1380</v>
       </c>
       <c r="M118" t="n">
-        <v>1952</v>
+        <v>1996</v>
       </c>
       <c r="N118" t="n">
         <v>7</v>
       </c>
       <c r="O118" t="n">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/North-Wales/124-Church-Rd-19454/home/38930705</t>
+          <t>https://www.redfin.com/PA/Horsham/315A-Olive-Ave-19044/home/147279844</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
@@ -10590,11 +10590,11 @@
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>PAMC2192188</t>
+          <t>PAMC2194122</t>
         </is>
       </c>
       <c r="U118" t="n">
-        <v>425000</v>
+        <v>429000</v>
       </c>
       <c r="V118" t="n">
         <v>0</v>
@@ -10608,17 +10608,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>315--A Olive Ave</t>
+          <t>120 Fairview Ave</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Horsham</t>
+          <t>Chalfont</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -10627,46 +10627,46 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>19044</v>
+        <v>18914</v>
       </c>
       <c r="G119" t="n">
-        <v>429000</v>
+        <v>429900</v>
       </c>
       <c r="H119" t="n">
         <v>3</v>
       </c>
       <c r="I119" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Horsham</t>
+          <t>Chalfont</t>
         </is>
       </c>
       <c r="K119" t="n">
-        <v>1620</v>
+        <v>1563</v>
       </c>
       <c r="L119" t="n">
-        <v>1380</v>
+        <v>10018</v>
       </c>
       <c r="M119" t="n">
-        <v>1996</v>
+        <v>1958</v>
       </c>
       <c r="N119" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O119" t="n">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="P119" t="inlineStr"/>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pre On-Market</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Horsham/315A-Olive-Ave-19044/home/147279844</t>
+          <t>https://www.redfin.com/PA/Chalfont/120-Fairview-Ave-18914/home/38564644</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
@@ -10676,11 +10676,11 @@
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>PAMC2194122</t>
+          <t>PABU2132014</t>
         </is>
       </c>
       <c r="U119" t="n">
-        <v>429000</v>
+        <v>429900</v>
       </c>
       <c r="V119" t="n">
         <v>0</v>
@@ -10739,7 +10739,7 @@
         <v>1920</v>
       </c>
       <c r="N120" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O120" t="n">
         <v>239</v>
@@ -10825,7 +10825,7 @@
         <v>1992</v>
       </c>
       <c r="N121" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O121" t="n">
         <v>227</v>
@@ -10913,7 +10913,7 @@
         <v>1982</v>
       </c>
       <c r="N122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O122" t="n">
         <v>254</v>
@@ -11087,7 +11087,7 @@
         <v>1977</v>
       </c>
       <c r="N124" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O124" t="n">
         <v>255</v>
@@ -11259,7 +11259,7 @@
         <v>1900</v>
       </c>
       <c r="N126" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O126" t="n">
         <v>146</v>
@@ -11345,7 +11345,7 @@
         <v>1952</v>
       </c>
       <c r="N127" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O127" t="n">
         <v>221</v>
@@ -11691,7 +11691,7 @@
         <v>1989</v>
       </c>
       <c r="N131" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O131" t="n">
         <v>209</v>
@@ -11779,7 +11779,7 @@
         <v>1973</v>
       </c>
       <c r="N132" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O132" t="n">
         <v>237</v>
@@ -12123,7 +12123,7 @@
         <v>1957</v>
       </c>
       <c r="N136" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O136" t="n">
         <v>267</v>
@@ -12209,7 +12209,7 @@
         <v>1950</v>
       </c>
       <c r="N137" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O137" t="n">
         <v>175</v>
@@ -12295,7 +12295,7 @@
         <v>1930</v>
       </c>
       <c r="N138" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O138" t="n">
         <v>213</v>
@@ -12553,7 +12553,7 @@
       </c>
       <c r="M141" t="inlineStr"/>
       <c r="N141" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O141" t="n">
         <v>241</v>
@@ -12903,7 +12903,7 @@
         <v>2003</v>
       </c>
       <c r="N145" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O145" t="n">
         <v>227</v>
@@ -12991,7 +12991,7 @@
         <v>1964</v>
       </c>
       <c r="N146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O146" t="n">
         <v>212</v>
@@ -13247,7 +13247,7 @@
         <v>1994</v>
       </c>
       <c r="N149" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O149" t="n">
         <v>241</v>
@@ -13335,7 +13335,7 @@
         <v>1998</v>
       </c>
       <c r="N150" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O150" t="n">
         <v>251</v>
@@ -13681,7 +13681,7 @@
         <v>1995</v>
       </c>
       <c r="N154" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O154" t="n">
         <v>164</v>
@@ -13769,7 +13769,7 @@
         <v>1998</v>
       </c>
       <c r="N155" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O155" t="n">
         <v>227</v>
@@ -14115,7 +14115,7 @@
         <v>1983</v>
       </c>
       <c r="N159" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O159" t="n">
         <v>299</v>
@@ -14203,7 +14203,7 @@
         <v>2000</v>
       </c>
       <c r="N160" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O160" t="n">
         <v>261</v>
@@ -14379,7 +14379,7 @@
         <v>1988</v>
       </c>
       <c r="N162" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O162" t="n">
         <v>225</v>
@@ -14467,7 +14467,7 @@
         <v>1997</v>
       </c>
       <c r="N163" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O163" t="n">
         <v>282</v>
@@ -14553,7 +14553,7 @@
         <v>1997</v>
       </c>
       <c r="N164" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O164" t="n">
         <v>201</v>
@@ -14641,7 +14641,7 @@
         <v>1952</v>
       </c>
       <c r="N165" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O165" t="n">
         <v>179</v>
@@ -14901,7 +14901,7 @@
         <v>1887</v>
       </c>
       <c r="N168" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O168" t="n">
         <v>246</v>
@@ -15071,7 +15071,7 @@
         <v>1965</v>
       </c>
       <c r="N170" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O170" t="n">
         <v>311</v>
@@ -15329,7 +15329,7 @@
         <v>1956</v>
       </c>
       <c r="N173" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O173" t="n">
         <v>295</v>
@@ -15537,7 +15537,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>MLS Listing</t>
+          <t>PAST SALE</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -15595,7 +15595,7 @@
       <c r="P176" t="inlineStr"/>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
@@ -15847,7 +15847,7 @@
         <v>1968</v>
       </c>
       <c r="N179" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O179" t="n">
         <v>228</v>
@@ -15933,7 +15933,7 @@
         <v>1935</v>
       </c>
       <c r="N180" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O180" t="n">
         <v>309</v>
@@ -16105,7 +16105,7 @@
         <v>1986</v>
       </c>
       <c r="N182" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O182" t="n">
         <v>232</v>
@@ -16279,7 +16279,7 @@
         <v>2023</v>
       </c>
       <c r="N184" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O184" t="n">
         <v>279</v>
@@ -16367,7 +16367,7 @@
         <v>2000</v>
       </c>
       <c r="N185" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O185" t="n">
         <v>202</v>
@@ -16455,7 +16455,7 @@
         <v>1994</v>
       </c>
       <c r="N186" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O186" t="n">
         <v>213</v>
@@ -16801,7 +16801,7 @@
         <v>1955</v>
       </c>
       <c r="N190" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O190" t="n">
         <v>204</v>
@@ -16973,7 +16973,7 @@
         <v>2017</v>
       </c>
       <c r="N192" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O192" t="n">
         <v>199</v>
@@ -17145,7 +17145,7 @@
         <v>1975</v>
       </c>
       <c r="N194" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O194" t="n">
         <v>302</v>
@@ -17407,7 +17407,7 @@
         <v>1960</v>
       </c>
       <c r="N197" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O197" t="n">
         <v>309</v>
@@ -18099,7 +18099,7 @@
         <v>1966</v>
       </c>
       <c r="N205" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O205" t="n">
         <v>264</v>
@@ -18185,7 +18185,7 @@
         <v>1955</v>
       </c>
       <c r="N206" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O206" t="n">
         <v>275</v>
@@ -18359,7 +18359,7 @@
         <v>1957</v>
       </c>
       <c r="N208" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O208" t="n">
         <v>199</v>
@@ -18445,7 +18445,7 @@
         <v>1915</v>
       </c>
       <c r="N209" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O209" t="n">
         <v>315</v>
@@ -18791,7 +18791,7 @@
         <v>1915</v>
       </c>
       <c r="N213" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O213" t="n">
         <v>265</v>
@@ -18873,7 +18873,7 @@
       </c>
       <c r="M214" t="inlineStr"/>
       <c r="N214" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O214" t="inlineStr"/>
       <c r="P214" t="inlineStr"/>
@@ -18955,7 +18955,7 @@
         <v>2003</v>
       </c>
       <c r="N215" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O215" t="n">
         <v>240</v>
@@ -19041,7 +19041,7 @@
         <v>1987</v>
       </c>
       <c r="N216" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O216" t="n">
         <v>235</v>
@@ -19051,7 +19051,7 @@
       </c>
       <c r="Q216" t="inlineStr">
         <is>
-          <t>Pre On-Market</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="R216" t="inlineStr">
@@ -19475,7 +19475,7 @@
         <v>1956</v>
       </c>
       <c r="N221" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O221" t="n">
         <v>253</v>
@@ -19647,7 +19647,7 @@
         <v>2020</v>
       </c>
       <c r="N223" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O223" t="n">
         <v>229</v>
@@ -19735,7 +19735,7 @@
         <v>1908</v>
       </c>
       <c r="N224" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O224" t="n">
         <v>204</v>
@@ -19995,7 +19995,7 @@
         <v>1987</v>
       </c>
       <c r="N227" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O227" t="n">
         <v>276</v>
@@ -20083,7 +20083,7 @@
         <v>1950</v>
       </c>
       <c r="N228" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O228" t="n">
         <v>270</v>
@@ -20429,7 +20429,7 @@
         <v>1920</v>
       </c>
       <c r="N232" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O232" t="n">
         <v>340</v>
@@ -20867,7 +20867,7 @@
         <v>1959</v>
       </c>
       <c r="N237" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O237" t="n">
         <v>252</v>
@@ -20953,7 +20953,7 @@
         <v>2003</v>
       </c>
       <c r="N238" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O238" t="n">
         <v>237</v>
@@ -21561,7 +21561,7 @@
         <v>1984</v>
       </c>
       <c r="N245" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O245" t="n">
         <v>273</v>
@@ -21823,7 +21823,7 @@
         <v>1995</v>
       </c>
       <c r="N248" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O248" t="n">
         <v>257</v>
@@ -22087,7 +22087,7 @@
         <v>1993</v>
       </c>
       <c r="N251" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O251" t="n">
         <v>324</v>
@@ -22259,7 +22259,7 @@
         <v>1961</v>
       </c>
       <c r="N253" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O253" t="n">
         <v>170</v>
@@ -22517,7 +22517,7 @@
         <v>2026</v>
       </c>
       <c r="N256" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O256" t="n">
         <v>271</v>
@@ -22601,7 +22601,7 @@
       <c r="L257" t="inlineStr"/>
       <c r="M257" t="inlineStr"/>
       <c r="N257" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O257" t="n">
         <v>271</v>
@@ -22689,7 +22689,7 @@
         <v>2000</v>
       </c>
       <c r="N258" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O258" t="n">
         <v>280</v>
@@ -22861,7 +22861,7 @@
         <v>1929</v>
       </c>
       <c r="N260" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O260" t="inlineStr"/>
       <c r="P260" t="inlineStr"/>
@@ -23381,7 +23381,7 @@
         <v>1918</v>
       </c>
       <c r="N266" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O266" t="n">
         <v>262</v>
@@ -23553,7 +23553,7 @@
         <v>1996</v>
       </c>
       <c r="N268" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O268" t="n">
         <v>264</v>
@@ -23641,7 +23641,7 @@
         <v>1961</v>
       </c>
       <c r="N269" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O269" t="n">
         <v>298</v>
@@ -23714,7 +23714,7 @@
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>Willow Grove</t>
+          <t>WILLOW MANOR</t>
         </is>
       </c>
       <c r="K270" t="n">
@@ -23727,7 +23727,7 @@
         <v>1949</v>
       </c>
       <c r="N270" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O270" t="n">
         <v>216</v>
@@ -23899,7 +23899,7 @@
         <v>2017</v>
       </c>
       <c r="N272" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O272" t="n">
         <v>258</v>
@@ -23987,7 +23987,7 @@
         <v>1988</v>
       </c>
       <c r="N273" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O273" t="n">
         <v>202</v>
@@ -24073,7 +24073,7 @@
         <v>1920</v>
       </c>
       <c r="N274" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O274" t="n">
         <v>233</v>
@@ -24159,7 +24159,7 @@
         <v>1962</v>
       </c>
       <c r="N275" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O275" t="n">
         <v>158</v>
@@ -24241,7 +24241,7 @@
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="inlineStr"/>
       <c r="N276" t="n">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="O276" t="n">
         <v>275</v>
@@ -24329,7 +24329,7 @@
         <v>1975</v>
       </c>
       <c r="N277" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O277" t="n">
         <v>281</v>
@@ -24415,7 +24415,7 @@
         <v>1889</v>
       </c>
       <c r="N278" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O278" t="n">
         <v>185</v>
@@ -24501,7 +24501,7 @@
         <v>2012</v>
       </c>
       <c r="N279" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O279" t="n">
         <v>239</v>
@@ -24589,7 +24589,7 @@
         <v>1964</v>
       </c>
       <c r="N280" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O280" t="n">
         <v>275</v>
@@ -24675,7 +24675,7 @@
         <v>1977</v>
       </c>
       <c r="N281" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O281" t="n">
         <v>235</v>
@@ -24847,7 +24847,7 @@
         <v>2022</v>
       </c>
       <c r="N283" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O283" t="n">
         <v>280</v>
@@ -24933,7 +24933,7 @@
       </c>
       <c r="M284" t="inlineStr"/>
       <c r="N284" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O284" t="n">
         <v>274</v>
@@ -25019,7 +25019,7 @@
         <v>2026</v>
       </c>
       <c r="N285" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O285" t="n">
         <v>274</v>
@@ -25105,7 +25105,7 @@
         <v>1957</v>
       </c>
       <c r="N286" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O286" t="n">
         <v>283</v>
@@ -25537,7 +25537,7 @@
         <v>1943</v>
       </c>
       <c r="N291" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O291" t="n">
         <v>239</v>
@@ -25621,7 +25621,7 @@
         <v>2026</v>
       </c>
       <c r="N292" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O292" t="n">
         <v>236</v>
@@ -25705,7 +25705,7 @@
       <c r="L293" t="inlineStr"/>
       <c r="M293" t="inlineStr"/>
       <c r="N293" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O293" t="n">
         <v>236</v>
@@ -25793,7 +25793,7 @@
         <v>1998</v>
       </c>
       <c r="N294" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O294" t="n">
         <v>276</v>
@@ -25879,7 +25879,7 @@
         <v>1951</v>
       </c>
       <c r="N295" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O295" t="n">
         <v>330</v>
@@ -26219,7 +26219,7 @@
         <v>1972</v>
       </c>
       <c r="N299" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O299" t="n">
         <v>256</v>
@@ -26305,7 +26305,7 @@
         <v>1993</v>
       </c>
       <c r="N300" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O300" t="n">
         <v>280</v>
@@ -26563,7 +26563,7 @@
         <v>1990</v>
       </c>
       <c r="N303" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O303" t="n">
         <v>183</v>
@@ -26651,7 +26651,7 @@
         <v>1910</v>
       </c>
       <c r="N304" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O304" t="n">
         <v>161</v>
@@ -26825,7 +26825,7 @@
         <v>2005</v>
       </c>
       <c r="N306" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O306" t="n">
         <v>267</v>
@@ -26913,7 +26913,7 @@
         <v>1860</v>
       </c>
       <c r="N307" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O307" t="n">
         <v>141</v>
@@ -27001,7 +27001,7 @@
         <v>2025</v>
       </c>
       <c r="N308" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O308" t="n">
         <v>267</v>
@@ -27089,7 +27089,7 @@
         <v>2025</v>
       </c>
       <c r="N309" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="O309" t="n">
         <v>267</v>
@@ -27177,7 +27177,7 @@
         <v>2025</v>
       </c>
       <c r="N310" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="O310" t="n">
         <v>267</v>
@@ -27265,7 +27265,7 @@
         <v>1997</v>
       </c>
       <c r="N311" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O311" t="n">
         <v>294</v>
@@ -27439,7 +27439,7 @@
         <v>1960</v>
       </c>
       <c r="N313" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O313" t="n">
         <v>328</v>
@@ -27523,7 +27523,7 @@
         <v>1974</v>
       </c>
       <c r="N314" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O314" t="n">
         <v>288</v>
@@ -27693,7 +27693,7 @@
         <v>1925</v>
       </c>
       <c r="N316" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O316" t="n">
         <v>275</v>
@@ -27777,7 +27777,7 @@
         <v>2026</v>
       </c>
       <c r="N317" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O317" t="n">
         <v>256</v>
@@ -28035,7 +28035,7 @@
         <v>1960</v>
       </c>
       <c r="N320" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O320" t="n">
         <v>338</v>
@@ -28121,7 +28121,7 @@
         <v>1955</v>
       </c>
       <c r="N321" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O321" t="n">
         <v>308</v>
@@ -28295,7 +28295,7 @@
         <v>1960</v>
       </c>
       <c r="N323" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O323" t="n">
         <v>276</v>
@@ -28381,7 +28381,7 @@
         <v>1972</v>
       </c>
       <c r="N324" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O324" t="n">
         <v>287</v>
@@ -28465,7 +28465,7 @@
         <v>2026</v>
       </c>
       <c r="N325" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O325" t="n">
         <v>292</v>
@@ -28553,7 +28553,7 @@
         <v>2025</v>
       </c>
       <c r="N326" t="n">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="O326" t="n">
         <v>271</v>
@@ -28641,7 +28641,7 @@
         <v>2005</v>
       </c>
       <c r="N327" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O327" t="n">
         <v>271</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="M328" t="inlineStr"/>
       <c r="N328" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="O328" t="n">
         <v>271</v>
@@ -28901,7 +28901,7 @@
         <v>2014</v>
       </c>
       <c r="N330" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O330" t="n">
         <v>371</v>
@@ -28987,7 +28987,7 @@
         <v>1918</v>
       </c>
       <c r="N331" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O331" t="n">
         <v>310</v>
@@ -29073,7 +29073,7 @@
         <v>1957</v>
       </c>
       <c r="N332" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O332" t="n">
         <v>318</v>
@@ -29245,7 +29245,7 @@
         <v>1950</v>
       </c>
       <c r="N334" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O334" t="n">
         <v>303</v>
@@ -29417,7 +29417,7 @@
         <v>1988</v>
       </c>
       <c r="N336" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O336" t="n">
         <v>190</v>
@@ -29505,7 +29505,7 @@
         <v>1923</v>
       </c>
       <c r="N337" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O337" t="n">
         <v>196</v>
@@ -29591,7 +29591,7 @@
         <v>1957</v>
       </c>
       <c r="N338" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O338" t="n">
         <v>204</v>
@@ -29677,7 +29677,7 @@
         <v>2022</v>
       </c>
       <c r="N339" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O339" t="n">
         <v>366</v>
@@ -29765,7 +29765,7 @@
         <v>1971</v>
       </c>
       <c r="N340" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O340" t="n">
         <v>298</v>
@@ -29851,7 +29851,7 @@
         <v>2019</v>
       </c>
       <c r="N341" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O341" t="n">
         <v>260</v>
@@ -29937,7 +29937,7 @@
         <v>2026</v>
       </c>
       <c r="N342" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O342" t="inlineStr"/>
       <c r="P342" t="inlineStr"/>
@@ -30017,7 +30017,7 @@
       <c r="L343" t="inlineStr"/>
       <c r="M343" t="inlineStr"/>
       <c r="N343" t="n">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="O343" t="n">
         <v>292</v>
@@ -30105,7 +30105,7 @@
         <v>2026</v>
       </c>
       <c r="N344" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="O344" t="n">
         <v>292</v>
@@ -30193,7 +30193,7 @@
         <v>2026</v>
       </c>
       <c r="N345" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="O345" t="n">
         <v>292</v>
@@ -30281,7 +30281,7 @@
         <v>2020</v>
       </c>
       <c r="N346" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O346" t="n">
         <v>283</v>
@@ -30369,7 +30369,7 @@
         <v>1914</v>
       </c>
       <c r="N347" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O347" t="n">
         <v>319</v>
@@ -30455,7 +30455,7 @@
         <v>2025</v>
       </c>
       <c r="N348" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="O348" t="n">
         <v>276</v>
@@ -30543,7 +30543,7 @@
         <v>1981</v>
       </c>
       <c r="N349" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O349" t="n">
         <v>253</v>
@@ -31231,7 +31231,7 @@
         <v>2021</v>
       </c>
       <c r="N357" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O357" t="n">
         <v>216</v>
@@ -31319,7 +31319,7 @@
         <v>1956</v>
       </c>
       <c r="N358" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O358" t="n">
         <v>268</v>
@@ -31405,7 +31405,7 @@
         <v>2020</v>
       </c>
       <c r="N359" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O359" t="n">
         <v>271</v>
@@ -31579,7 +31579,7 @@
         <v>1980</v>
       </c>
       <c r="N361" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O361" t="n">
         <v>231</v>
@@ -31837,7 +31837,7 @@
       </c>
       <c r="M364" t="inlineStr"/>
       <c r="N364" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O364" t="n">
         <v>271</v>
@@ -31925,7 +31925,7 @@
         <v>1969</v>
       </c>
       <c r="N365" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O365" t="n">
         <v>300</v>
@@ -32009,7 +32009,7 @@
         <v>2026</v>
       </c>
       <c r="N366" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O366" t="n">
         <v>271</v>
@@ -32093,7 +32093,7 @@
         <v>2026</v>
       </c>
       <c r="N367" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O367" t="n">
         <v>271</v>
@@ -32177,7 +32177,7 @@
         <v>2026</v>
       </c>
       <c r="N368" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O368" t="n">
         <v>271</v>
@@ -32349,7 +32349,7 @@
         <v>1998</v>
       </c>
       <c r="N370" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O370" t="n">
         <v>251</v>
@@ -32613,7 +32613,7 @@
         <v>1950</v>
       </c>
       <c r="N373" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O373" t="n">
         <v>200</v>
@@ -32785,7 +32785,7 @@
         <v>2026</v>
       </c>
       <c r="N375" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O375" t="n">
         <v>352</v>
@@ -33127,7 +33127,7 @@
         <v>2026</v>
       </c>
       <c r="N379" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O379" t="n">
         <v>257</v>
@@ -33215,7 +33215,7 @@
         <v>1959</v>
       </c>
       <c r="N380" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O380" t="n">
         <v>272</v>
@@ -33301,7 +33301,7 @@
         <v>1978</v>
       </c>
       <c r="N381" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O381" t="n">
         <v>397</v>
@@ -33387,7 +33387,7 @@
         <v>1999</v>
       </c>
       <c r="N382" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O382" t="n">
         <v>161</v>
@@ -33425,22 +33425,22 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>PAST SALE</t>
+          <t>MLS Listing</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>110 Meadow View Ln</t>
+          <t>735 E Township Line Rd</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Lansdale</t>
+          <t>Blue Bell</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -33449,10 +33449,10 @@
         </is>
       </c>
       <c r="F383" t="n">
-        <v>19446</v>
+        <v>19422</v>
       </c>
       <c r="G383" t="n">
-        <v>599999</v>
+        <v>600000</v>
       </c>
       <c r="H383" t="n">
         <v>4</v>
@@ -33462,35 +33462,33 @@
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>CENTER POINT FARM</t>
+          <t>Blue Bell</t>
         </is>
       </c>
       <c r="K383" t="n">
-        <v>3472</v>
+        <v>2832</v>
       </c>
       <c r="L383" t="n">
-        <v>1872</v>
+        <v>83200</v>
       </c>
       <c r="M383" t="n">
-        <v>2000</v>
+        <v>1992</v>
       </c>
       <c r="N383" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="O383" t="n">
-        <v>173</v>
-      </c>
-      <c r="P383" t="n">
-        <v>350</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="P383" t="inlineStr"/>
       <c r="Q383" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Contingent</t>
         </is>
       </c>
       <c r="R383" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Lansdale/110-Meadow-View-Ln-19446/home/39128121</t>
+          <t>https://www.redfin.com/PA/Blue-Bell/735-E-Township-Line-Rd-19422/home/39121059</t>
         </is>
       </c>
       <c r="S383" t="inlineStr">
@@ -33500,11 +33498,11 @@
       </c>
       <c r="T383" t="inlineStr">
         <is>
-          <t>PAMC2186924</t>
+          <t>PAMC2191776</t>
         </is>
       </c>
       <c r="U383" t="n">
-        <v>599999</v>
+        <v>600000</v>
       </c>
       <c r="V383" t="n">
         <v>0</v>
@@ -33523,12 +33521,12 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>735 E Township Line Rd</t>
+          <t>745 Crestview Blvd</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Blue Bell</t>
+          <t>Collegeville</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -33537,46 +33535,48 @@
         </is>
       </c>
       <c r="F384" t="n">
-        <v>19422</v>
+        <v>19426</v>
       </c>
       <c r="G384" t="n">
         <v>600000</v>
       </c>
       <c r="H384" t="n">
+        <v>3</v>
+      </c>
+      <c r="I384" t="n">
+        <v>3</v>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>THE MEADOWS AT SKI</t>
+        </is>
+      </c>
+      <c r="K384" t="n">
+        <v>3007</v>
+      </c>
+      <c r="L384" t="n">
+        <v>13641</v>
+      </c>
+      <c r="M384" t="n">
+        <v>2004</v>
+      </c>
+      <c r="N384" t="n">
         <v>4</v>
       </c>
-      <c r="I384" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J384" t="inlineStr">
-        <is>
-          <t>Blue Bell</t>
-        </is>
-      </c>
-      <c r="K384" t="n">
-        <v>2832</v>
-      </c>
-      <c r="L384" t="n">
-        <v>83200</v>
-      </c>
-      <c r="M384" t="n">
-        <v>1992</v>
-      </c>
-      <c r="N384" t="n">
-        <v>10</v>
-      </c>
       <c r="O384" t="n">
-        <v>212</v>
-      </c>
-      <c r="P384" t="inlineStr"/>
+        <v>200</v>
+      </c>
+      <c r="P384" t="n">
+        <v>288</v>
+      </c>
       <c r="Q384" t="inlineStr">
         <is>
-          <t>Contingent</t>
+          <t>Pre On-Market</t>
         </is>
       </c>
       <c r="R384" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Blue-Bell/735-E-Township-Line-Rd-19422/home/39121059</t>
+          <t>https://www.redfin.com/PA/Collegeville/745-Crestview-Blvd-19426/home/37961731</t>
         </is>
       </c>
       <c r="S384" t="inlineStr">
@@ -33586,7 +33586,7 @@
       </c>
       <c r="T384" t="inlineStr">
         <is>
-          <t>PAMC2191776</t>
+          <t>PAMC2196186</t>
         </is>
       </c>
       <c r="U384" t="n">
@@ -33609,12 +33609,12 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>745 Crestview Blvd</t>
+          <t>805 Harston Ln</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Collegeville</t>
+          <t>Erdenheim</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -33623,7 +33623,7 @@
         </is>
       </c>
       <c r="F385" t="n">
-        <v>19426</v>
+        <v>19038</v>
       </c>
       <c r="G385" t="n">
         <v>600000</v>
@@ -33636,35 +33636,33 @@
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>THE MEADOWS AT SKI</t>
+          <t>ERDENHEIM</t>
         </is>
       </c>
       <c r="K385" t="n">
-        <v>3007</v>
+        <v>3560</v>
       </c>
       <c r="L385" t="n">
-        <v>13641</v>
+        <v>25300</v>
       </c>
       <c r="M385" t="n">
-        <v>2004</v>
+        <v>1955</v>
       </c>
       <c r="N385" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="O385" t="n">
-        <v>200</v>
-      </c>
-      <c r="P385" t="n">
-        <v>288</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="P385" t="inlineStr"/>
       <c r="Q385" t="inlineStr">
         <is>
-          <t>Pre On-Market</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="R385" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Collegeville/745-Crestview-Blvd-19426/home/37961731</t>
+          <t>https://www.redfin.com/PA/Erdenheim/805-Harston-Ln-19038/home/38822898</t>
         </is>
       </c>
       <c r="S385" t="inlineStr">
@@ -33674,7 +33672,7 @@
       </c>
       <c r="T385" t="inlineStr">
         <is>
-          <t>PAMC2196186</t>
+          <t>PAMC2194642</t>
         </is>
       </c>
       <c r="U385" t="n">
@@ -33687,7 +33685,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>MLS Listing</t>
+          <t>PAST SALE</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -33697,12 +33695,12 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>805 Harston Ln</t>
+          <t>400 E Prospect Ave</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Erdenheim</t>
+          <t>North Wales</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -33711,46 +33709,46 @@
         </is>
       </c>
       <c r="F386" t="n">
-        <v>19038</v>
+        <v>19454</v>
       </c>
       <c r="G386" t="n">
         <v>600000</v>
       </c>
       <c r="H386" t="n">
+        <v>4</v>
+      </c>
+      <c r="I386" t="n">
+        <v>2</v>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>North Wales</t>
+        </is>
+      </c>
+      <c r="K386" t="n">
+        <v>2250</v>
+      </c>
+      <c r="L386" t="n">
+        <v>12700</v>
+      </c>
+      <c r="M386" t="n">
+        <v>1930</v>
+      </c>
+      <c r="N386" t="n">
         <v>3</v>
       </c>
-      <c r="I386" t="n">
-        <v>3</v>
-      </c>
-      <c r="J386" t="inlineStr">
-        <is>
-          <t>ERDENHEIM</t>
-        </is>
-      </c>
-      <c r="K386" t="n">
-        <v>3560</v>
-      </c>
-      <c r="L386" t="n">
-        <v>25300</v>
-      </c>
-      <c r="M386" t="n">
-        <v>1955</v>
-      </c>
-      <c r="N386" t="n">
-        <v>16</v>
-      </c>
       <c r="O386" t="n">
-        <v>169</v>
+        <v>267</v>
       </c>
       <c r="P386" t="inlineStr"/>
       <c r="Q386" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="R386" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Erdenheim/805-Harston-Ln-19038/home/38822898</t>
+          <t>https://www.redfin.com/PA/North-Wales/400-E-Prospect-Ave-19454/home/38126497</t>
         </is>
       </c>
       <c r="S386" t="inlineStr">
@@ -33760,7 +33758,7 @@
       </c>
       <c r="T386" t="inlineStr">
         <is>
-          <t>PAMC2194642</t>
+          <t>PAMC2194404</t>
         </is>
       </c>
       <c r="U386" t="n">
@@ -33773,7 +33771,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>PAST SALE</t>
+          <t>MLS Listing</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -33783,12 +33781,12 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>400 E Prospect Ave</t>
+          <t>0 Lamott Ave</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>North Wales</t>
+          <t>Willow Grove</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -33797,46 +33795,42 @@
         </is>
       </c>
       <c r="F387" t="n">
-        <v>19454</v>
+        <v>19090</v>
       </c>
       <c r="G387" t="n">
         <v>600000</v>
       </c>
       <c r="H387" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I387" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>North Wales</t>
-        </is>
-      </c>
-      <c r="K387" t="n">
-        <v>2250</v>
-      </c>
+          <t>CRESTMONT</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr"/>
       <c r="L387" t="n">
-        <v>12700</v>
+        <v>5182</v>
       </c>
       <c r="M387" t="n">
-        <v>1930</v>
+        <v>2026</v>
       </c>
       <c r="N387" t="n">
-        <v>3</v>
-      </c>
-      <c r="O387" t="n">
-        <v>267</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="O387" t="inlineStr"/>
       <c r="P387" t="inlineStr"/>
       <c r="Q387" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="R387" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/North-Wales/400-E-Prospect-Ave-19454/home/38126497</t>
+          <t>https://www.redfin.com/PA/Willow-Grove/Lamott-Ave-19090/home/38226900</t>
         </is>
       </c>
       <c r="S387" t="inlineStr">
@@ -33846,7 +33840,7 @@
       </c>
       <c r="T387" t="inlineStr">
         <is>
-          <t>PAMC2194404</t>
+          <t>PAMC2170730</t>
         </is>
       </c>
       <c r="U387" t="n">
@@ -33867,14 +33861,10 @@
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="C388" t="inlineStr">
-        <is>
-          <t>0 Lamott Ave</t>
-        </is>
-      </c>
+      <c r="C388" t="inlineStr"/>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Willow Grove</t>
+          <t>Blue Bell</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -33883,132 +33873,54 @@
         </is>
       </c>
       <c r="F388" t="n">
-        <v>19090</v>
-      </c>
-      <c r="G388" t="n">
-        <v>600000</v>
-      </c>
+        <v>19422</v>
+      </c>
+      <c r="G388" t="inlineStr"/>
       <c r="H388" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I388" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J388" t="inlineStr">
-        <is>
-          <t>CRESTMONT</t>
-        </is>
-      </c>
-      <c r="K388" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="J388" t="inlineStr"/>
+      <c r="K388" t="n">
+        <v>2800</v>
+      </c>
       <c r="L388" t="n">
-        <v>5182</v>
+        <v>25920</v>
       </c>
       <c r="M388" t="n">
-        <v>2026</v>
+        <v>1958</v>
       </c>
       <c r="N388" t="n">
-        <v>201</v>
+        <v>17</v>
       </c>
       <c r="O388" t="inlineStr"/>
       <c r="P388" t="inlineStr"/>
       <c r="Q388" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Pre On-Market</t>
         </is>
       </c>
       <c r="R388" t="inlineStr">
         <is>
-          <t>https://www.redfin.com/PA/Willow-Grove/Lamott-Ave-19090/home/38226900</t>
+          <t>https://www.redfin.com/PA/Blue-Bell/Undisclosed-address-19422/home/39124645</t>
         </is>
       </c>
       <c r="S388" t="inlineStr">
         <is>
-          <t>BRIGHT MLS</t>
+          <t>Compass International Holdings</t>
         </is>
       </c>
       <c r="T388" t="inlineStr">
         <is>
-          <t>PAMC2170730</t>
+          <t>2196674563876010737</t>
         </is>
       </c>
       <c r="U388" t="n">
-        <v>600000</v>
+        <v>0</v>
       </c>
       <c r="V388" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>MLS Listing</t>
-        </is>
-      </c>
-      <c r="B389" t="inlineStr">
-        <is>
-          <t>Single Family Residential</t>
-        </is>
-      </c>
-      <c r="C389" t="inlineStr"/>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>Blue Bell</t>
-        </is>
-      </c>
-      <c r="E389" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="F389" t="n">
-        <v>19422</v>
-      </c>
-      <c r="G389" t="inlineStr"/>
-      <c r="H389" t="n">
-        <v>4</v>
-      </c>
-      <c r="I389" t="n">
-        <v>4</v>
-      </c>
-      <c r="J389" t="inlineStr"/>
-      <c r="K389" t="n">
-        <v>2800</v>
-      </c>
-      <c r="L389" t="n">
-        <v>25920</v>
-      </c>
-      <c r="M389" t="n">
-        <v>1958</v>
-      </c>
-      <c r="N389" t="n">
-        <v>16</v>
-      </c>
-      <c r="O389" t="inlineStr"/>
-      <c r="P389" t="inlineStr"/>
-      <c r="Q389" t="inlineStr">
-        <is>
-          <t>Pre On-Market</t>
-        </is>
-      </c>
-      <c r="R389" t="inlineStr">
-        <is>
-          <t>https://www.redfin.com/PA/Blue-Bell/Undisclosed-address-19422/home/39124645</t>
-        </is>
-      </c>
-      <c r="S389" t="inlineStr">
-        <is>
-          <t>Compass International Holdings</t>
-        </is>
-      </c>
-      <c r="T389" t="inlineStr">
-        <is>
-          <t>2196674563876010737</t>
-        </is>
-      </c>
-      <c r="U389" t="n">
-        <v>0</v>
-      </c>
-      <c r="V389" t="n">
         <v>0</v>
       </c>
     </row>
